--- a/Financial Analysis/CEG.xlsx
+++ b/Financial Analysis/CEG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A2F881-0BF3-446B-84C3-D56DB0681D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AEA03C-D25E-42C2-88CB-76A3DDD8BFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FD8B9579-E08E-4C89-8726-3FC953CC4FC9}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t>CEG</t>
   </si>
@@ -137,6 +137,93 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>PPA Margin</t>
+  </si>
+  <si>
+    <t>Maintenance Margin</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Net cash</t>
+  </si>
+  <si>
+    <t>Per share</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>Consensus</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
+  </si>
+  <si>
+    <t>Restricted cash</t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t>Derivatives</t>
+  </si>
+  <si>
+    <t>Inventories</t>
+  </si>
+  <si>
+    <t>Credits</t>
+  </si>
+  <si>
+    <t>OCA</t>
+  </si>
+  <si>
+    <t>Current assets</t>
+  </si>
+  <si>
+    <t>PP&amp;E</t>
+  </si>
+  <si>
+    <t>Investments</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>ONCA</t>
+  </si>
+  <si>
+    <t>Non-current assets</t>
+  </si>
+  <si>
+    <t>Total assets</t>
   </si>
 </sst>
 </file>
@@ -197,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -214,6 +301,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -229,6 +317,111 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{633D4322-3274-D79C-C184-51727DCB0288}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12908280" y="7620"/>
+          <a:ext cx="0" cy="6073140"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A33F0183-3FE8-BA84-79D4-6F19517AC87E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8031480" y="15240"/>
+          <a:ext cx="0" cy="6065520"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -528,24 +721,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A70581-6FBD-4939-B80C-3CABCD009FA4}">
-  <dimension ref="B2:H9"/>
+  <dimension ref="B2:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="8" width="14.21875" style="3" customWidth="1"/>
+    <col min="5" max="7" width="14.21875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,70 +746,80 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>285.52</v>
+        <v>332.45</v>
+      </c>
+      <c r="E3" s="4">
+        <v>45909</v>
       </c>
       <c r="F3" s="4">
-        <v>45571</v>
+        <f ca="1">TODAY()</f>
+        <v>45927</v>
       </c>
       <c r="G3" s="4">
-        <f ca="1">TODAY()</f>
-        <v>45770</v>
-      </c>
-      <c r="H3" s="4">
-        <v>45601</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+        <v>45971</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>213.7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+        <f>312.4</f>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>61015.623999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+        <v>103857.37999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>311+72+584</f>
-        <v>967</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+        <f>1974+88</f>
+        <v>2062</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>680+1035+7409</f>
-        <v>9124</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+        <f>900+125+7286</f>
+        <v>8311</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-8157</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+        <v>-6249</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>69172.623999999996</v>
+        <v>110106.37999999999</v>
       </c>
     </row>
   </sheetData>
@@ -626,13 +829,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4841C5-2D92-4E0E-A023-57C39442136D}">
-  <dimension ref="B2:N23"/>
+  <dimension ref="B2:EJ42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:140" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
@@ -657,475 +861,2996 @@
       <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L2">
+      <c r="K2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="Q2">
         <v>2021</v>
       </c>
-      <c r="M2">
+      <c r="R2">
         <v>2022</v>
       </c>
-      <c r="N2">
+      <c r="S2">
         <v>2023</v>
       </c>
-    </row>
-    <row r="3" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T2">
+        <v>2024</v>
+      </c>
+      <c r="U2">
+        <v>2025</v>
+      </c>
+      <c r="V2">
+        <v>2026</v>
+      </c>
+      <c r="W2">
+        <v>2027</v>
+      </c>
+      <c r="X2">
+        <v>2028</v>
+      </c>
+      <c r="Y2">
+        <v>2029</v>
+      </c>
+      <c r="Z2">
+        <v>2030</v>
+      </c>
+      <c r="AA2">
+        <v>2031</v>
+      </c>
+      <c r="AB2">
+        <v>2032</v>
+      </c>
+      <c r="AC2">
+        <v>2033</v>
+      </c>
+      <c r="AD2">
+        <v>2034</v>
+      </c>
+      <c r="AE2">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="3" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C3" s="8">
+        <v>7565</v>
+      </c>
       <c r="D3" s="8">
         <v>5446</v>
       </c>
+      <c r="E3" s="8">
+        <v>6111</v>
+      </c>
+      <c r="F3" s="8">
+        <f>S3-E3-D3-C3</f>
+        <v>5796</v>
+      </c>
+      <c r="G3" s="8">
+        <v>6161</v>
+      </c>
       <c r="H3" s="8">
         <v>5475</v>
       </c>
+      <c r="I3" s="8">
+        <v>6550</v>
+      </c>
+      <c r="J3" s="8">
+        <f>T3-I3-H3-G3</f>
+        <v>5382</v>
+      </c>
+      <c r="K3" s="8">
+        <v>6788</v>
+      </c>
       <c r="L3" s="8">
+        <v>6101</v>
+      </c>
+      <c r="M3" s="8">
+        <v>7000</v>
+      </c>
+      <c r="N3" s="8">
+        <f>J3*1.1</f>
+        <v>5920.2000000000007</v>
+      </c>
+      <c r="Q3" s="8">
         <v>19649</v>
       </c>
-      <c r="M3" s="8">
+      <c r="R3" s="8">
         <f>24280+160</f>
         <v>24440</v>
       </c>
-      <c r="N3" s="8">
+      <c r="S3" s="8">
         <v>24918</v>
       </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T3" s="8">
+        <v>23568</v>
+      </c>
+      <c r="U3" s="8">
+        <f>SUM(K3:N3)</f>
+        <v>25809.200000000001</v>
+      </c>
+      <c r="V3" s="8">
+        <f>U3*1.09</f>
+        <v>28132.028000000002</v>
+      </c>
+      <c r="W3" s="8">
+        <f>V3*1.08</f>
+        <v>30382.590240000005</v>
+      </c>
+      <c r="X3" s="8">
+        <f>W3*1.06</f>
+        <v>32205.545654400008</v>
+      </c>
+      <c r="Y3" s="8">
+        <f>X3*1.05</f>
+        <v>33815.822937120007</v>
+      </c>
+      <c r="Z3" s="8">
+        <f>Y3*1.04</f>
+        <v>35168.455854604807</v>
+      </c>
+      <c r="AA3" s="8">
+        <f t="shared" ref="AA3:AE3" si="0">Z3*1.03</f>
+        <v>36223.509530242954</v>
+      </c>
+      <c r="AB3" s="8">
+        <f t="shared" si="0"/>
+        <v>37310.214816150241</v>
+      </c>
+      <c r="AC3" s="8">
+        <f t="shared" si="0"/>
+        <v>38429.521260634749</v>
+      </c>
+      <c r="AD3" s="8">
+        <f t="shared" si="0"/>
+        <v>39582.406898453795</v>
+      </c>
+      <c r="AE3" s="8">
+        <f t="shared" si="0"/>
+        <v>40769.87910540741</v>
+      </c>
+    </row>
+    <row r="4" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>12</v>
       </c>
+      <c r="C4" s="5">
+        <v>5729</v>
+      </c>
       <c r="D4" s="5">
         <v>2887</v>
       </c>
+      <c r="E4" s="5">
+        <v>3367</v>
+      </c>
+      <c r="F4" s="5">
+        <f>S4-E4-D4-C4</f>
+        <v>4018</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3417</v>
+      </c>
       <c r="H4" s="5">
         <v>2292</v>
       </c>
+      <c r="I4" s="5">
+        <v>3119</v>
+      </c>
+      <c r="J4" s="5">
+        <f>T4-I4-H4-G4</f>
+        <v>2591</v>
+      </c>
+      <c r="K4" s="5">
+        <v>4384</v>
+      </c>
       <c r="L4" s="5">
+        <v>3132</v>
+      </c>
+      <c r="M4" s="5">
+        <f>M3*0.55</f>
+        <v>3850.0000000000005</v>
+      </c>
+      <c r="N4" s="5">
+        <f>N3*0.55</f>
+        <v>3256.1100000000006</v>
+      </c>
+      <c r="Q4" s="5">
         <f>12157+6</f>
         <v>12163</v>
       </c>
-      <c r="M4" s="5">
+      <c r="R4" s="5">
         <f>17457+5</f>
         <v>17462</v>
       </c>
-      <c r="N4" s="5">
+      <c r="S4" s="5">
         <v>16001</v>
       </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T4" s="5">
+        <v>11419</v>
+      </c>
+      <c r="U4" s="5">
+        <f>SUM(K4:N4)</f>
+        <v>14622.11</v>
+      </c>
+      <c r="V4" s="5">
+        <f>V3*0.56</f>
+        <v>15753.935680000002</v>
+      </c>
+      <c r="W4" s="5">
+        <f t="shared" ref="W4:AE4" si="1">W3*0.56</f>
+        <v>17014.250534400006</v>
+      </c>
+      <c r="X4" s="5">
+        <f t="shared" si="1"/>
+        <v>18035.105566464008</v>
+      </c>
+      <c r="Y4" s="5">
+        <f t="shared" si="1"/>
+        <v>18936.860844787207</v>
+      </c>
+      <c r="Z4" s="5">
+        <f t="shared" si="1"/>
+        <v>19694.335278578692</v>
+      </c>
+      <c r="AA4" s="5">
+        <f t="shared" si="1"/>
+        <v>20285.165336936057</v>
+      </c>
+      <c r="AB4" s="5">
+        <f t="shared" si="1"/>
+        <v>20893.720297044136</v>
+      </c>
+      <c r="AC4" s="5">
+        <f t="shared" si="1"/>
+        <v>21520.53190595546</v>
+      </c>
+      <c r="AD4" s="5">
+        <f t="shared" si="1"/>
+        <v>22166.147863134127</v>
+      </c>
+      <c r="AE4" s="5">
+        <f t="shared" si="1"/>
+        <v>22831.132299028151</v>
+      </c>
+    </row>
+    <row r="5" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>13</v>
       </c>
+      <c r="C5" s="5">
+        <v>1432</v>
+      </c>
       <c r="D5" s="5">
         <v>1477</v>
       </c>
+      <c r="E5" s="5">
+        <v>1353</v>
+      </c>
+      <c r="F5" s="5">
+        <f>S5-E5-D5-C5</f>
+        <v>1423</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1486</v>
+      </c>
       <c r="H5" s="5">
         <v>1645</v>
       </c>
+      <c r="I5" s="5">
+        <v>1535</v>
+      </c>
+      <c r="J5" s="5">
+        <f>T5-I5-H5-G5</f>
+        <v>1493</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1545</v>
+      </c>
       <c r="L5" s="5">
+        <v>1617</v>
+      </c>
+      <c r="M5" s="5">
+        <f>M3*0.25</f>
+        <v>1750</v>
+      </c>
+      <c r="N5" s="5">
+        <f>N3*0.25</f>
+        <v>1480.0500000000002</v>
+      </c>
+      <c r="Q5" s="5">
         <f>3934+621</f>
         <v>4555</v>
       </c>
-      <c r="M5" s="5">
+      <c r="R5" s="5">
         <f>4797+44</f>
         <v>4841</v>
       </c>
-      <c r="N5" s="5">
+      <c r="S5" s="5">
         <v>5685</v>
       </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T5" s="5">
+        <v>6159</v>
+      </c>
+      <c r="U5" s="5">
+        <f>SUM(K5:N5)</f>
+        <v>6392.05</v>
+      </c>
+      <c r="V5" s="5">
+        <f>V3*0.23</f>
+        <v>6470.3664400000007</v>
+      </c>
+      <c r="W5" s="5">
+        <f t="shared" ref="W5:AE5" si="2">W3*0.23</f>
+        <v>6987.9957552000014</v>
+      </c>
+      <c r="X5" s="5">
+        <f t="shared" si="2"/>
+        <v>7407.2755005120025</v>
+      </c>
+      <c r="Y5" s="5">
+        <f t="shared" si="2"/>
+        <v>7777.6392755376019</v>
+      </c>
+      <c r="Z5" s="5">
+        <f t="shared" si="2"/>
+        <v>8088.744846559106</v>
+      </c>
+      <c r="AA5" s="5">
+        <f t="shared" si="2"/>
+        <v>8331.4071919558792</v>
+      </c>
+      <c r="AB5" s="5">
+        <f t="shared" si="2"/>
+        <v>8581.3494077145551</v>
+      </c>
+      <c r="AC5" s="5">
+        <f t="shared" si="2"/>
+        <v>8838.7898899459924</v>
+      </c>
+      <c r="AD5" s="5">
+        <f t="shared" si="2"/>
+        <v>9103.953586644373</v>
+      </c>
+      <c r="AE5" s="5">
+        <f t="shared" si="2"/>
+        <v>9377.0721942437049</v>
+      </c>
+    </row>
+    <row r="6" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>32</v>
       </c>
+      <c r="C6" s="5">
+        <f t="shared" ref="C6:L6" si="3">C4+C5</f>
+        <v>7161</v>
+      </c>
       <c r="D6" s="5">
-        <f>D4+D5</f>
+        <f t="shared" si="3"/>
         <v>4364</v>
       </c>
+      <c r="E6" s="5">
+        <f t="shared" si="3"/>
+        <v>4720</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="3"/>
+        <v>5441</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="3"/>
+        <v>4903</v>
+      </c>
       <c r="H6" s="5">
-        <f>H4+H5</f>
+        <f t="shared" si="3"/>
         <v>3937</v>
       </c>
+      <c r="I6" s="5">
+        <f t="shared" si="3"/>
+        <v>4654</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="3"/>
+        <v>4084</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="3"/>
+        <v>5929</v>
+      </c>
       <c r="L6" s="5">
-        <f>L4+L5</f>
+        <f t="shared" si="3"/>
+        <v>4749</v>
+      </c>
+      <c r="M6" s="5">
+        <f t="shared" ref="M6:N6" si="4">M4+M5</f>
+        <v>5600</v>
+      </c>
+      <c r="N6" s="5">
+        <f t="shared" si="4"/>
+        <v>4736.1600000000008</v>
+      </c>
+      <c r="Q6" s="5">
+        <f t="shared" ref="Q6:V6" si="5">Q4+Q5</f>
         <v>16718</v>
       </c>
-      <c r="M6" s="5">
-        <f>M4+M5</f>
+      <c r="R6" s="5">
+        <f t="shared" si="5"/>
         <v>22303</v>
       </c>
-      <c r="N6" s="5">
-        <f>N4+N5</f>
+      <c r="S6" s="5">
+        <f t="shared" si="5"/>
         <v>21686</v>
       </c>
-    </row>
-    <row r="7" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T6" s="5">
+        <f t="shared" si="5"/>
+        <v>17578</v>
+      </c>
+      <c r="U6" s="5">
+        <f t="shared" si="5"/>
+        <v>21014.16</v>
+      </c>
+      <c r="V6" s="5">
+        <f t="shared" si="5"/>
+        <v>22224.302120000004</v>
+      </c>
+      <c r="W6" s="5">
+        <f t="shared" ref="W6:AE6" si="6">W4+W5</f>
+        <v>24002.246289600007</v>
+      </c>
+      <c r="X6" s="5">
+        <f t="shared" si="6"/>
+        <v>25442.38106697601</v>
+      </c>
+      <c r="Y6" s="5">
+        <f t="shared" si="6"/>
+        <v>26714.50012032481</v>
+      </c>
+      <c r="Z6" s="5">
+        <f t="shared" si="6"/>
+        <v>27783.0801251378</v>
+      </c>
+      <c r="AA6" s="5">
+        <f t="shared" si="6"/>
+        <v>28616.572528891935</v>
+      </c>
+      <c r="AB6" s="5">
+        <f t="shared" si="6"/>
+        <v>29475.069704758691</v>
+      </c>
+      <c r="AC6" s="5">
+        <f t="shared" si="6"/>
+        <v>30359.321795901451</v>
+      </c>
+      <c r="AD6" s="5">
+        <f t="shared" si="6"/>
+        <v>31270.1014497785</v>
+      </c>
+      <c r="AE6" s="5">
+        <f t="shared" si="6"/>
+        <v>32208.204493271856</v>
+      </c>
+    </row>
+    <row r="7" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="C7" s="8">
+        <f t="shared" ref="C7:L7" si="7">C3-C6</f>
+        <v>404</v>
+      </c>
       <c r="D7" s="8">
-        <f>D3-D6</f>
+        <f t="shared" si="7"/>
         <v>1082</v>
       </c>
+      <c r="E7" s="8">
+        <f t="shared" si="7"/>
+        <v>1391</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="7"/>
+        <v>355</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="7"/>
+        <v>1258</v>
+      </c>
       <c r="H7" s="8">
-        <f>H3-H6</f>
+        <f t="shared" si="7"/>
         <v>1538</v>
       </c>
+      <c r="I7" s="8">
+        <f t="shared" si="7"/>
+        <v>1896</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="7"/>
+        <v>1298</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="7"/>
+        <v>859</v>
+      </c>
       <c r="L7" s="8">
-        <f>L3-L6</f>
+        <f t="shared" si="7"/>
+        <v>1352</v>
+      </c>
+      <c r="M7" s="8">
+        <f t="shared" ref="M7:N7" si="8">M3-M6</f>
+        <v>1400</v>
+      </c>
+      <c r="N7" s="8">
+        <f t="shared" si="8"/>
+        <v>1184.04</v>
+      </c>
+      <c r="Q7" s="8">
+        <f t="shared" ref="Q7:V7" si="9">Q3-Q6</f>
         <v>2931</v>
       </c>
-      <c r="M7" s="8">
-        <f>M3-M6</f>
+      <c r="R7" s="8">
+        <f t="shared" si="9"/>
         <v>2137</v>
       </c>
-      <c r="N7" s="8">
-        <f>N3-N6</f>
+      <c r="S7" s="8">
+        <f t="shared" si="9"/>
         <v>3232</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T7" s="8">
+        <f t="shared" si="9"/>
+        <v>5990</v>
+      </c>
+      <c r="U7" s="8">
+        <f t="shared" si="9"/>
+        <v>4795.0400000000009</v>
+      </c>
+      <c r="V7" s="8">
+        <f t="shared" si="9"/>
+        <v>5907.7258799999981</v>
+      </c>
+      <c r="W7" s="8">
+        <f t="shared" ref="W7:AE7" si="10">W3-W6</f>
+        <v>6380.343950399998</v>
+      </c>
+      <c r="X7" s="8">
+        <f t="shared" si="10"/>
+        <v>6763.1645874239985</v>
+      </c>
+      <c r="Y7" s="8">
+        <f t="shared" si="10"/>
+        <v>7101.3228167951966</v>
+      </c>
+      <c r="Z7" s="8">
+        <f t="shared" si="10"/>
+        <v>7385.3757294670067</v>
+      </c>
+      <c r="AA7" s="8">
+        <f t="shared" si="10"/>
+        <v>7606.9370013510197</v>
+      </c>
+      <c r="AB7" s="8">
+        <f t="shared" si="10"/>
+        <v>7835.14511139155</v>
+      </c>
+      <c r="AC7" s="8">
+        <f t="shared" si="10"/>
+        <v>8070.1994647332976</v>
+      </c>
+      <c r="AD7" s="8">
+        <f t="shared" si="10"/>
+        <v>8312.3054486752953</v>
+      </c>
+      <c r="AE7" s="8">
+        <f t="shared" si="10"/>
+        <v>8561.6746121355536</v>
+      </c>
+    </row>
+    <row r="8" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>14</v>
       </c>
+      <c r="C8" s="5">
+        <v>267</v>
+      </c>
       <c r="D8" s="5">
         <v>274</v>
       </c>
+      <c r="E8" s="5">
+        <v>266</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" ref="F8:F9" si="11">S8-E8-D8-C8</f>
+        <v>289</v>
+      </c>
+      <c r="G8" s="5">
+        <v>306</v>
+      </c>
       <c r="H8" s="5">
         <v>296</v>
       </c>
+      <c r="I8" s="5">
+        <v>266</v>
+      </c>
+      <c r="J8" s="5">
+        <f>T8-I8-H8-G8</f>
+        <v>255</v>
+      </c>
+      <c r="K8" s="5">
+        <v>248</v>
+      </c>
       <c r="L8" s="5">
+        <v>254</v>
+      </c>
+      <c r="M8" s="5">
+        <f>I8*1.03</f>
+        <v>273.98</v>
+      </c>
+      <c r="N8" s="5">
+        <f>J8*1.03</f>
+        <v>262.65000000000003</v>
+      </c>
+      <c r="Q8" s="5">
         <v>3003</v>
       </c>
-      <c r="M8" s="5">
+      <c r="R8" s="5">
         <v>1091</v>
       </c>
-      <c r="N8" s="5">
+      <c r="S8" s="5">
         <v>1096</v>
       </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T8" s="5">
+        <v>1123</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" ref="U8:U9" si="12">SUM(K8:N8)</f>
+        <v>1038.6300000000001</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>15</v>
       </c>
+      <c r="C9" s="5">
+        <v>132</v>
+      </c>
       <c r="D9" s="5">
         <v>139</v>
       </c>
+      <c r="E9" s="5">
+        <v>148</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="11"/>
+        <v>134</v>
+      </c>
+      <c r="G9" s="5">
+        <v>139</v>
+      </c>
       <c r="H9" s="5">
         <v>142</v>
       </c>
+      <c r="I9" s="5">
+        <v>165</v>
+      </c>
+      <c r="J9" s="5">
+        <f>T9-I9-H9-G9</f>
+        <v>140</v>
+      </c>
+      <c r="K9" s="5">
+        <v>160</v>
+      </c>
       <c r="L9" s="5">
+        <v>147</v>
+      </c>
+      <c r="M9" s="5">
+        <f>M7*0.12</f>
+        <v>168</v>
+      </c>
+      <c r="N9" s="5">
+        <f>N7*0.12</f>
+        <v>142.0848</v>
+      </c>
+      <c r="Q9" s="5">
         <v>475</v>
       </c>
-      <c r="M9" s="5">
+      <c r="R9" s="5">
         <v>552</v>
       </c>
-      <c r="N9" s="5">
+      <c r="S9" s="5">
         <v>553</v>
       </c>
-    </row>
-    <row r="10" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T9" s="5">
+        <v>586</v>
+      </c>
+      <c r="U9" s="5">
+        <f t="shared" si="12"/>
+        <v>617.08479999999997</v>
+      </c>
+      <c r="V9" s="5">
+        <f>V7*0.12</f>
+        <v>708.92710559999978</v>
+      </c>
+      <c r="W9" s="5">
+        <f t="shared" ref="W9:AE9" si="13">W7*0.12</f>
+        <v>765.64127404799979</v>
+      </c>
+      <c r="X9" s="5">
+        <f t="shared" si="13"/>
+        <v>811.57975049087975</v>
+      </c>
+      <c r="Y9" s="5">
+        <f t="shared" si="13"/>
+        <v>852.15873801542352</v>
+      </c>
+      <c r="Z9" s="5">
+        <f t="shared" si="13"/>
+        <v>886.24508753604073</v>
+      </c>
+      <c r="AA9" s="5">
+        <f t="shared" si="13"/>
+        <v>912.83244016212234</v>
+      </c>
+      <c r="AB9" s="5">
+        <f t="shared" si="13"/>
+        <v>940.21741336698597</v>
+      </c>
+      <c r="AC9" s="5">
+        <f t="shared" si="13"/>
+        <v>968.42393576799566</v>
+      </c>
+      <c r="AD9" s="5">
+        <f t="shared" si="13"/>
+        <v>997.47665384103539</v>
+      </c>
+      <c r="AE9" s="5">
+        <f t="shared" si="13"/>
+        <v>1027.4009534562665</v>
+      </c>
+    </row>
+    <row r="10" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="C10" s="8">
+        <f t="shared" ref="C10:L10" si="14">C7-C8-C9</f>
+        <v>5</v>
+      </c>
       <c r="D10" s="8">
-        <f>D7-D8-D9</f>
+        <f t="shared" si="14"/>
         <v>669</v>
       </c>
+      <c r="E10" s="8">
+        <f t="shared" si="14"/>
+        <v>977</v>
+      </c>
+      <c r="F10" s="8">
+        <f t="shared" si="14"/>
+        <v>-68</v>
+      </c>
+      <c r="G10" s="8">
+        <f t="shared" si="14"/>
+        <v>813</v>
+      </c>
       <c r="H10" s="8">
-        <f>H7-H8-H9</f>
+        <f t="shared" si="14"/>
         <v>1100</v>
       </c>
+      <c r="I10" s="8">
+        <f t="shared" si="14"/>
+        <v>1465</v>
+      </c>
+      <c r="J10" s="8">
+        <f t="shared" si="14"/>
+        <v>903</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="14"/>
+        <v>451</v>
+      </c>
       <c r="L10" s="8">
-        <f>L7-L8-L9</f>
+        <f t="shared" si="14"/>
+        <v>951</v>
+      </c>
+      <c r="M10" s="8">
+        <f t="shared" ref="M10:N10" si="15">M7-M8-M9</f>
+        <v>958.02</v>
+      </c>
+      <c r="N10" s="8">
+        <f t="shared" si="15"/>
+        <v>779.3051999999999</v>
+      </c>
+      <c r="Q10" s="8">
+        <f t="shared" ref="Q10:V10" si="16">Q7-Q8-Q9</f>
         <v>-547</v>
       </c>
-      <c r="M10" s="8">
-        <f>M7-M8-M9</f>
+      <c r="R10" s="8">
+        <f t="shared" si="16"/>
         <v>494</v>
       </c>
-      <c r="N10" s="8">
-        <f>N7-N8-N9</f>
+      <c r="S10" s="8">
+        <f t="shared" si="16"/>
         <v>1583</v>
       </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T10" s="8">
+        <f t="shared" si="16"/>
+        <v>4281</v>
+      </c>
+      <c r="U10" s="8">
+        <f t="shared" si="16"/>
+        <v>3139.3252000000007</v>
+      </c>
+      <c r="V10" s="8">
+        <f t="shared" si="16"/>
+        <v>5198.7987743999984</v>
+      </c>
+      <c r="W10" s="8">
+        <f t="shared" ref="W10:AE10" si="17">W7-W8-W9</f>
+        <v>5614.702676351998</v>
+      </c>
+      <c r="X10" s="8">
+        <f t="shared" si="17"/>
+        <v>5951.5848369331188</v>
+      </c>
+      <c r="Y10" s="8">
+        <f t="shared" si="17"/>
+        <v>6249.1640787797733</v>
+      </c>
+      <c r="Z10" s="8">
+        <f t="shared" si="17"/>
+        <v>6499.1306419309658</v>
+      </c>
+      <c r="AA10" s="8">
+        <f t="shared" si="17"/>
+        <v>6694.1045611888976</v>
+      </c>
+      <c r="AB10" s="8">
+        <f t="shared" si="17"/>
+        <v>6894.9276980245641</v>
+      </c>
+      <c r="AC10" s="8">
+        <f t="shared" si="17"/>
+        <v>7101.7755289653023</v>
+      </c>
+      <c r="AD10" s="8">
+        <f t="shared" si="17"/>
+        <v>7314.8287948342604</v>
+      </c>
+      <c r="AE10" s="8">
+        <f t="shared" si="17"/>
+        <v>7534.2736586792871</v>
+      </c>
+    </row>
+    <row r="11" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>16</v>
       </c>
+      <c r="C11" s="5">
+        <v>107</v>
+      </c>
       <c r="D11" s="5">
         <v>103</v>
       </c>
+      <c r="E11" s="5">
+        <v>82</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" ref="F11:F12" si="18">S11-E11-D11-C11</f>
+        <v>139</v>
+      </c>
+      <c r="G11" s="5">
+        <v>127</v>
+      </c>
       <c r="H11" s="5">
         <v>142</v>
       </c>
+      <c r="I11" s="5">
+        <v>147</v>
+      </c>
+      <c r="J11" s="5">
+        <f>T11-I11-H11-G11</f>
+        <v>90</v>
+      </c>
+      <c r="K11" s="5">
+        <v>146</v>
+      </c>
       <c r="L11" s="5">
+        <v>118</v>
+      </c>
+      <c r="M11" s="5">
+        <f>I11*1.02</f>
+        <v>149.94</v>
+      </c>
+      <c r="N11" s="5">
+        <f>J11*1.02</f>
+        <v>91.8</v>
+      </c>
+      <c r="Q11" s="5">
         <f>282+15</f>
         <v>297</v>
       </c>
-      <c r="M11" s="5">
+      <c r="R11" s="5">
         <v>251</v>
       </c>
-      <c r="N11" s="5">
+      <c r="S11" s="5">
         <v>431</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T11" s="5">
+        <v>506</v>
+      </c>
+      <c r="U11" s="5">
+        <f t="shared" ref="U11:U12" si="19">SUM(K11:N11)</f>
+        <v>505.74</v>
+      </c>
+      <c r="V11" s="5">
+        <f>U11*1.01</f>
+        <v>510.79740000000004</v>
+      </c>
+      <c r="W11" s="5">
+        <f t="shared" ref="W11:AE11" si="20">V11*1.01</f>
+        <v>515.90537400000005</v>
+      </c>
+      <c r="X11" s="5">
+        <f t="shared" si="20"/>
+        <v>521.06442774000004</v>
+      </c>
+      <c r="Y11" s="5">
+        <f t="shared" si="20"/>
+        <v>526.27507201740002</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="20"/>
+        <v>531.53782273757406</v>
+      </c>
+      <c r="AA11" s="5">
+        <f t="shared" si="20"/>
+        <v>536.85320096494979</v>
+      </c>
+      <c r="AB11" s="5">
+        <f t="shared" si="20"/>
+        <v>542.22173297459926</v>
+      </c>
+      <c r="AC11" s="5">
+        <f t="shared" si="20"/>
+        <v>547.64395030434525</v>
+      </c>
+      <c r="AD11" s="5">
+        <f t="shared" si="20"/>
+        <v>553.12038980738873</v>
+      </c>
+      <c r="AE11" s="5">
+        <f t="shared" si="20"/>
+        <v>558.65159370546257</v>
+      </c>
+    </row>
+    <row r="12" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>17</v>
       </c>
+      <c r="C12" s="5">
+        <f>-314-26</f>
+        <v>-340</v>
+      </c>
       <c r="D12" s="5">
         <v>-605</v>
       </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="18"/>
+        <v>-350</v>
+      </c>
+      <c r="G12" s="5">
+        <v>-362</v>
+      </c>
       <c r="H12" s="5">
         <v>-6</v>
       </c>
+      <c r="I12" s="5">
+        <f>-325-2</f>
+        <v>-327</v>
+      </c>
+      <c r="J12" s="5">
+        <f>T12-I12-H12-G12</f>
+        <v>-46</v>
+      </c>
+      <c r="K12" s="5">
+        <v>154</v>
+      </c>
       <c r="L12" s="5">
+        <v>-440</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5">
         <f>-795-201</f>
         <v>-996</v>
       </c>
-      <c r="M12" s="5">
+      <c r="R12" s="5">
         <f>786-1</f>
         <v>785</v>
       </c>
-      <c r="N12" s="5">
+      <c r="S12" s="5">
         <f>-1268-27</f>
         <v>-1295</v>
       </c>
-    </row>
-    <row r="13" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T12" s="5">
+        <f>-670-71</f>
+        <v>-741</v>
+      </c>
+      <c r="U12" s="5">
+        <f t="shared" si="19"/>
+        <v>-286</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C13" s="8">
+        <f t="shared" ref="C13:N13" si="21">C10-C11-C12</f>
+        <v>238</v>
+      </c>
       <c r="D13" s="8">
-        <f>D10-D11-D12</f>
+        <f t="shared" si="21"/>
         <v>1171</v>
       </c>
+      <c r="E13" s="8">
+        <f t="shared" si="21"/>
+        <v>895</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="21"/>
+        <v>143</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="21"/>
+        <v>1048</v>
+      </c>
       <c r="H13" s="8">
-        <f>H10-H11-H12</f>
+        <f t="shared" si="21"/>
         <v>964</v>
       </c>
+      <c r="I13" s="8">
+        <f t="shared" si="21"/>
+        <v>1645</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="21"/>
+        <v>859</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="21"/>
+        <v>151</v>
+      </c>
       <c r="L13" s="8">
-        <f>L10-L11-L12</f>
+        <f t="shared" si="21"/>
+        <v>1273</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" si="21"/>
+        <v>808.07999999999993</v>
+      </c>
+      <c r="N13" s="8">
+        <f t="shared" si="21"/>
+        <v>687.50519999999995</v>
+      </c>
+      <c r="Q13" s="8">
+        <f t="shared" ref="Q13:V13" si="22">Q10-Q11-Q12</f>
         <v>152</v>
       </c>
-      <c r="M13" s="8">
-        <f>M10-M11-M12</f>
+      <c r="R13" s="8">
+        <f t="shared" si="22"/>
         <v>-542</v>
       </c>
-      <c r="N13" s="8">
-        <f>N10-N11-N12</f>
+      <c r="S13" s="8">
+        <f t="shared" si="22"/>
         <v>2447</v>
       </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T13" s="8">
+        <f t="shared" si="22"/>
+        <v>4516</v>
+      </c>
+      <c r="U13" s="8">
+        <f t="shared" si="22"/>
+        <v>2919.5852000000004</v>
+      </c>
+      <c r="V13" s="8">
+        <f t="shared" si="22"/>
+        <v>4688.001374399998</v>
+      </c>
+      <c r="W13" s="8">
+        <f t="shared" ref="W13:AE13" si="23">W10-W11-W12</f>
+        <v>5098.797302351998</v>
+      </c>
+      <c r="X13" s="8">
+        <f t="shared" si="23"/>
+        <v>5430.5204091931191</v>
+      </c>
+      <c r="Y13" s="8">
+        <f t="shared" si="23"/>
+        <v>5722.8890067623734</v>
+      </c>
+      <c r="Z13" s="8">
+        <f t="shared" si="23"/>
+        <v>5967.5928191933917</v>
+      </c>
+      <c r="AA13" s="8">
+        <f t="shared" si="23"/>
+        <v>6157.2513602239478</v>
+      </c>
+      <c r="AB13" s="8">
+        <f t="shared" si="23"/>
+        <v>6352.705965049965</v>
+      </c>
+      <c r="AC13" s="8">
+        <f t="shared" si="23"/>
+        <v>6554.1315786609575</v>
+      </c>
+      <c r="AD13" s="8">
+        <f t="shared" si="23"/>
+        <v>6761.7084050268713</v>
+      </c>
+      <c r="AE13" s="8">
+        <f t="shared" si="23"/>
+        <v>6975.6220649738243</v>
+      </c>
+    </row>
+    <row r="14" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>19</v>
       </c>
+      <c r="C14" s="5">
+        <v>131</v>
+      </c>
       <c r="D14" s="5">
         <v>342</v>
       </c>
+      <c r="E14" s="5">
+        <v>205</v>
+      </c>
+      <c r="F14" s="5">
+        <f>S14-E14-D14-C14</f>
+        <v>181</v>
+      </c>
+      <c r="G14" s="5">
+        <v>165</v>
+      </c>
       <c r="H14" s="5">
         <v>154</v>
       </c>
+      <c r="I14" s="5">
+        <v>449</v>
+      </c>
+      <c r="J14" s="5">
+        <f>T14-I14-H14-G14</f>
+        <v>6</v>
+      </c>
+      <c r="K14" s="5">
+        <v>22</v>
+      </c>
       <c r="L14" s="5">
+        <v>440</v>
+      </c>
+      <c r="M14" s="5">
+        <f>M13*0.17</f>
+        <v>137.37360000000001</v>
+      </c>
+      <c r="N14" s="5">
+        <f>N13*0.17</f>
+        <v>116.875884</v>
+      </c>
+      <c r="Q14" s="5">
         <v>-225</v>
       </c>
-      <c r="M14" s="5">
+      <c r="R14" s="5">
         <v>-388</v>
       </c>
-      <c r="N14" s="5">
+      <c r="S14" s="5">
         <v>859</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T14" s="5">
+        <v>774</v>
+      </c>
+      <c r="U14" s="5">
+        <f>SUM(K14:N14)</f>
+        <v>716.24948400000005</v>
+      </c>
+      <c r="V14" s="5">
+        <f>V13*0.17</f>
+        <v>796.96023364799976</v>
+      </c>
+      <c r="W14" s="5">
+        <f t="shared" ref="W14:AE14" si="24">W13*0.17</f>
+        <v>866.79554139983975</v>
+      </c>
+      <c r="X14" s="5">
+        <f t="shared" si="24"/>
+        <v>923.18846956283028</v>
+      </c>
+      <c r="Y14" s="5">
+        <f t="shared" si="24"/>
+        <v>972.89113114960355</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" si="24"/>
+        <v>1014.4907792628767</v>
+      </c>
+      <c r="AA14" s="5">
+        <f t="shared" si="24"/>
+        <v>1046.7327312380712</v>
+      </c>
+      <c r="AB14" s="5">
+        <f t="shared" si="24"/>
+        <v>1079.9600140584942</v>
+      </c>
+      <c r="AC14" s="5">
+        <f t="shared" si="24"/>
+        <v>1114.2023683723628</v>
+      </c>
+      <c r="AD14" s="5">
+        <f t="shared" si="24"/>
+        <v>1149.4904288545681</v>
+      </c>
+      <c r="AE14" s="5">
+        <f t="shared" si="24"/>
+        <v>1185.8557510455503</v>
+      </c>
+    </row>
+    <row r="15" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C15" s="8">
+        <f t="shared" ref="C15:N15" si="25">C13-C14</f>
+        <v>107</v>
+      </c>
       <c r="D15" s="8">
-        <f>D13-D14</f>
+        <f t="shared" si="25"/>
         <v>829</v>
       </c>
+      <c r="E15" s="8">
+        <f t="shared" si="25"/>
+        <v>690</v>
+      </c>
+      <c r="F15" s="8">
+        <f t="shared" si="25"/>
+        <v>-38</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="25"/>
+        <v>883</v>
+      </c>
       <c r="H15" s="8">
-        <f>H13-H14</f>
+        <f t="shared" si="25"/>
         <v>810</v>
       </c>
+      <c r="I15" s="8">
+        <f t="shared" si="25"/>
+        <v>1196</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="25"/>
+        <v>853</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" si="25"/>
+        <v>129</v>
+      </c>
       <c r="L15" s="8">
-        <f>L13-L14</f>
+        <f t="shared" si="25"/>
+        <v>833</v>
+      </c>
+      <c r="M15" s="8">
+        <f t="shared" si="25"/>
+        <v>670.70639999999992</v>
+      </c>
+      <c r="N15" s="8">
+        <f t="shared" si="25"/>
+        <v>570.6293159999999</v>
+      </c>
+      <c r="Q15" s="8">
+        <f t="shared" ref="Q15:V15" si="26">Q13-Q14</f>
         <v>377</v>
       </c>
-      <c r="M15" s="8">
-        <f>M13-M14</f>
+      <c r="R15" s="8">
+        <f t="shared" si="26"/>
         <v>-154</v>
       </c>
-      <c r="N15" s="8">
-        <f>N13-N14</f>
+      <c r="S15" s="8">
+        <f t="shared" si="26"/>
         <v>1588</v>
       </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T15" s="8">
+        <f t="shared" si="26"/>
+        <v>3742</v>
+      </c>
+      <c r="U15" s="8">
+        <f t="shared" si="26"/>
+        <v>2203.3357160000005</v>
+      </c>
+      <c r="V15" s="8">
+        <f t="shared" si="26"/>
+        <v>3891.0411407519982</v>
+      </c>
+      <c r="W15" s="8">
+        <f t="shared" ref="W15:AE15" si="27">W13-W14</f>
+        <v>4232.0017609521583</v>
+      </c>
+      <c r="X15" s="8">
+        <f t="shared" si="27"/>
+        <v>4507.3319396302886</v>
+      </c>
+      <c r="Y15" s="8">
+        <f t="shared" si="27"/>
+        <v>4749.9978756127693</v>
+      </c>
+      <c r="Z15" s="8">
+        <f t="shared" si="27"/>
+        <v>4953.1020399305153</v>
+      </c>
+      <c r="AA15" s="8">
+        <f t="shared" si="27"/>
+        <v>5110.5186289858766</v>
+      </c>
+      <c r="AB15" s="8">
+        <f t="shared" si="27"/>
+        <v>5272.7459509914706</v>
+      </c>
+      <c r="AC15" s="8">
+        <f t="shared" si="27"/>
+        <v>5439.9292102885947</v>
+      </c>
+      <c r="AD15" s="8">
+        <f t="shared" si="27"/>
+        <v>5612.2179761723037</v>
+      </c>
+      <c r="AE15" s="8">
+        <f t="shared" si="27"/>
+        <v>5789.766313928274</v>
+      </c>
+      <c r="AF15" s="1">
+        <f>AE15*(1+$AH$20)</f>
+        <v>5731.8686507889915</v>
+      </c>
+      <c r="AG15" s="1">
+        <f t="shared" ref="AG15:CR15" si="28">AF15*(1+$AH$20)</f>
+        <v>5674.5499642811019</v>
+      </c>
+      <c r="AH15" s="1">
+        <f t="shared" si="28"/>
+        <v>5617.8044646382905</v>
+      </c>
+      <c r="AI15" s="1">
+        <f t="shared" si="28"/>
+        <v>5561.6264199919078</v>
+      </c>
+      <c r="AJ15" s="1">
+        <f t="shared" si="28"/>
+        <v>5506.0101557919888</v>
+      </c>
+      <c r="AK15" s="1">
+        <f t="shared" si="28"/>
+        <v>5450.9500542340693</v>
+      </c>
+      <c r="AL15" s="1">
+        <f t="shared" si="28"/>
+        <v>5396.4405536917284</v>
+      </c>
+      <c r="AM15" s="1">
+        <f t="shared" si="28"/>
+        <v>5342.4761481548112</v>
+      </c>
+      <c r="AN15" s="1">
+        <f t="shared" si="28"/>
+        <v>5289.0513866732626</v>
+      </c>
+      <c r="AO15" s="1">
+        <f t="shared" si="28"/>
+        <v>5236.1608728065303</v>
+      </c>
+      <c r="AP15" s="1">
+        <f t="shared" si="28"/>
+        <v>5183.7992640784651</v>
+      </c>
+      <c r="AQ15" s="1">
+        <f t="shared" si="28"/>
+        <v>5131.9612714376808</v>
+      </c>
+      <c r="AR15" s="1">
+        <f t="shared" si="28"/>
+        <v>5080.6416587233043</v>
+      </c>
+      <c r="AS15" s="1">
+        <f t="shared" si="28"/>
+        <v>5029.8352421360714</v>
+      </c>
+      <c r="AT15" s="1">
+        <f t="shared" si="28"/>
+        <v>4979.5368897147109</v>
+      </c>
+      <c r="AU15" s="1">
+        <f t="shared" si="28"/>
+        <v>4929.7415208175635</v>
+      </c>
+      <c r="AV15" s="1">
+        <f t="shared" si="28"/>
+        <v>4880.4441056093874</v>
+      </c>
+      <c r="AW15" s="1">
+        <f t="shared" si="28"/>
+        <v>4831.6396645532932</v>
+      </c>
+      <c r="AX15" s="1">
+        <f t="shared" si="28"/>
+        <v>4783.3232679077601</v>
+      </c>
+      <c r="AY15" s="1">
+        <f t="shared" si="28"/>
+        <v>4735.4900352286822</v>
+      </c>
+      <c r="AZ15" s="1">
+        <f t="shared" si="28"/>
+        <v>4688.1351348763956</v>
+      </c>
+      <c r="BA15" s="1">
+        <f t="shared" si="28"/>
+        <v>4641.2537835276316</v>
+      </c>
+      <c r="BB15" s="1">
+        <f t="shared" si="28"/>
+        <v>4594.8412456923552</v>
+      </c>
+      <c r="BC15" s="1">
+        <f t="shared" si="28"/>
+        <v>4548.8928332354317</v>
+      </c>
+      <c r="BD15" s="1">
+        <f t="shared" si="28"/>
+        <v>4503.4039049030771</v>
+      </c>
+      <c r="BE15" s="1">
+        <f t="shared" si="28"/>
+        <v>4458.3698658540461</v>
+      </c>
+      <c r="BF15" s="1">
+        <f t="shared" si="28"/>
+        <v>4413.7861671955052</v>
+      </c>
+      <c r="BG15" s="1">
+        <f t="shared" si="28"/>
+        <v>4369.6483055235503</v>
+      </c>
+      <c r="BH15" s="1">
+        <f t="shared" si="28"/>
+        <v>4325.9518224683152</v>
+      </c>
+      <c r="BI15" s="1">
+        <f t="shared" si="28"/>
+        <v>4282.692304243632</v>
+      </c>
+      <c r="BJ15" s="1">
+        <f t="shared" si="28"/>
+        <v>4239.8653812011953</v>
+      </c>
+      <c r="BK15" s="1">
+        <f t="shared" si="28"/>
+        <v>4197.4667273891837</v>
+      </c>
+      <c r="BL15" s="1">
+        <f t="shared" si="28"/>
+        <v>4155.4920601152917</v>
+      </c>
+      <c r="BM15" s="1">
+        <f t="shared" si="28"/>
+        <v>4113.9371395141388</v>
+      </c>
+      <c r="BN15" s="1">
+        <f t="shared" si="28"/>
+        <v>4072.7977681189973</v>
+      </c>
+      <c r="BO15" s="1">
+        <f t="shared" si="28"/>
+        <v>4032.0697904378071</v>
+      </c>
+      <c r="BP15" s="1">
+        <f t="shared" si="28"/>
+        <v>3991.7490925334291</v>
+      </c>
+      <c r="BQ15" s="1">
+        <f t="shared" si="28"/>
+        <v>3951.8316016080948</v>
+      </c>
+      <c r="BR15" s="1">
+        <f t="shared" si="28"/>
+        <v>3912.3132855920139</v>
+      </c>
+      <c r="BS15" s="1">
+        <f t="shared" si="28"/>
+        <v>3873.1901527360938</v>
+      </c>
+      <c r="BT15" s="1">
+        <f t="shared" si="28"/>
+        <v>3834.4582512087327</v>
+      </c>
+      <c r="BU15" s="1">
+        <f t="shared" si="28"/>
+        <v>3796.1136686966452</v>
+      </c>
+      <c r="BV15" s="1">
+        <f t="shared" si="28"/>
+        <v>3758.1525320096785</v>
+      </c>
+      <c r="BW15" s="1">
+        <f t="shared" si="28"/>
+        <v>3720.5710066895817</v>
+      </c>
+      <c r="BX15" s="1">
+        <f t="shared" si="28"/>
+        <v>3683.3652966226859</v>
+      </c>
+      <c r="BY15" s="1">
+        <f t="shared" si="28"/>
+        <v>3646.531643656459</v>
+      </c>
+      <c r="BZ15" s="1">
+        <f t="shared" si="28"/>
+        <v>3610.0663272198944</v>
+      </c>
+      <c r="CA15" s="1">
+        <f t="shared" si="28"/>
+        <v>3573.9656639476952</v>
+      </c>
+      <c r="CB15" s="1">
+        <f t="shared" si="28"/>
+        <v>3538.2260073082184</v>
+      </c>
+      <c r="CC15" s="1">
+        <f t="shared" si="28"/>
+        <v>3502.8437472351361</v>
+      </c>
+      <c r="CD15" s="1">
+        <f t="shared" si="28"/>
+        <v>3467.8153097627846</v>
+      </c>
+      <c r="CE15" s="1">
+        <f t="shared" si="28"/>
+        <v>3433.1371566651569</v>
+      </c>
+      <c r="CF15" s="1">
+        <f t="shared" si="28"/>
+        <v>3398.8057850985051</v>
+      </c>
+      <c r="CG15" s="1">
+        <f t="shared" si="28"/>
+        <v>3364.81772724752</v>
+      </c>
+      <c r="CH15" s="1">
+        <f t="shared" si="28"/>
+        <v>3331.1695499750449</v>
+      </c>
+      <c r="CI15" s="1">
+        <f t="shared" si="28"/>
+        <v>3297.8578544752945</v>
+      </c>
+      <c r="CJ15" s="1">
+        <f t="shared" si="28"/>
+        <v>3264.8792759305416</v>
+      </c>
+      <c r="CK15" s="1">
+        <f t="shared" si="28"/>
+        <v>3232.2304831712363</v>
+      </c>
+      <c r="CL15" s="1">
+        <f t="shared" si="28"/>
+        <v>3199.9081783395241</v>
+      </c>
+      <c r="CM15" s="1">
+        <f t="shared" si="28"/>
+        <v>3167.9090965561286</v>
+      </c>
+      <c r="CN15" s="1">
+        <f t="shared" si="28"/>
+        <v>3136.2300055905671</v>
+      </c>
+      <c r="CO15" s="1">
+        <f t="shared" si="28"/>
+        <v>3104.8677055346616</v>
+      </c>
+      <c r="CP15" s="1">
+        <f t="shared" si="28"/>
+        <v>3073.819028479315</v>
+      </c>
+      <c r="CQ15" s="1">
+        <f t="shared" si="28"/>
+        <v>3043.0808381945217</v>
+      </c>
+      <c r="CR15" s="1">
+        <f t="shared" si="28"/>
+        <v>3012.6500298125766</v>
+      </c>
+      <c r="CS15" s="1">
+        <f t="shared" ref="CS15:EJ15" si="29">CR15*(1+$AH$20)</f>
+        <v>2982.5235295144507</v>
+      </c>
+      <c r="CT15" s="1">
+        <f t="shared" si="29"/>
+        <v>2952.6982942193063</v>
+      </c>
+      <c r="CU15" s="1">
+        <f t="shared" si="29"/>
+        <v>2923.1713112771131</v>
+      </c>
+      <c r="CV15" s="1">
+        <f t="shared" si="29"/>
+        <v>2893.939598164342</v>
+      </c>
+      <c r="CW15" s="1">
+        <f t="shared" si="29"/>
+        <v>2865.0002021826986</v>
+      </c>
+      <c r="CX15" s="1">
+        <f t="shared" si="29"/>
+        <v>2836.3502001608717</v>
+      </c>
+      <c r="CY15" s="1">
+        <f t="shared" si="29"/>
+        <v>2807.9866981592631</v>
+      </c>
+      <c r="CZ15" s="1">
+        <f t="shared" si="29"/>
+        <v>2779.9068311776705</v>
+      </c>
+      <c r="DA15" s="1">
+        <f t="shared" si="29"/>
+        <v>2752.1077628658936</v>
+      </c>
+      <c r="DB15" s="1">
+        <f t="shared" si="29"/>
+        <v>2724.5866852372346</v>
+      </c>
+      <c r="DC15" s="1">
+        <f t="shared" si="29"/>
+        <v>2697.3408183848624</v>
+      </c>
+      <c r="DD15" s="1">
+        <f t="shared" si="29"/>
+        <v>2670.3674102010136</v>
+      </c>
+      <c r="DE15" s="1">
+        <f t="shared" si="29"/>
+        <v>2643.6637360990035</v>
+      </c>
+      <c r="DF15" s="1">
+        <f t="shared" si="29"/>
+        <v>2617.2270987380134</v>
+      </c>
+      <c r="DG15" s="1">
+        <f t="shared" si="29"/>
+        <v>2591.0548277506332</v>
+      </c>
+      <c r="DH15" s="1">
+        <f t="shared" si="29"/>
+        <v>2565.144279473127</v>
+      </c>
+      <c r="DI15" s="1">
+        <f t="shared" si="29"/>
+        <v>2539.4928366783956</v>
+      </c>
+      <c r="DJ15" s="1">
+        <f t="shared" si="29"/>
+        <v>2514.0979083116117</v>
+      </c>
+      <c r="DK15" s="1">
+        <f t="shared" si="29"/>
+        <v>2488.9569292284955</v>
+      </c>
+      <c r="DL15" s="1">
+        <f t="shared" si="29"/>
+        <v>2464.0673599362103</v>
+      </c>
+      <c r="DM15" s="1">
+        <f t="shared" si="29"/>
+        <v>2439.426686336848</v>
+      </c>
+      <c r="DN15" s="1">
+        <f t="shared" si="29"/>
+        <v>2415.0324194734794</v>
+      </c>
+      <c r="DO15" s="1">
+        <f t="shared" si="29"/>
+        <v>2390.8820952787446</v>
+      </c>
+      <c r="DP15" s="1">
+        <f t="shared" si="29"/>
+        <v>2366.9732743259569</v>
+      </c>
+      <c r="DQ15" s="1">
+        <f t="shared" si="29"/>
+        <v>2343.3035415826976</v>
+      </c>
+      <c r="DR15" s="1">
+        <f t="shared" si="29"/>
+        <v>2319.8705061668707</v>
+      </c>
+      <c r="DS15" s="1">
+        <f t="shared" si="29"/>
+        <v>2296.6718011052021</v>
+      </c>
+      <c r="DT15" s="1">
+        <f t="shared" si="29"/>
+        <v>2273.7050830941503</v>
+      </c>
+      <c r="DU15" s="1">
+        <f t="shared" si="29"/>
+        <v>2250.9680322632089</v>
+      </c>
+      <c r="DV15" s="1">
+        <f t="shared" si="29"/>
+        <v>2228.4583519405769</v>
+      </c>
+      <c r="DW15" s="1">
+        <f t="shared" si="29"/>
+        <v>2206.1737684211712</v>
+      </c>
+      <c r="DX15" s="1">
+        <f t="shared" si="29"/>
+        <v>2184.1120307369592</v>
+      </c>
+      <c r="DY15" s="1">
+        <f t="shared" si="29"/>
+        <v>2162.2709104295895</v>
+      </c>
+      <c r="DZ15" s="1">
+        <f t="shared" si="29"/>
+        <v>2140.6482013252935</v>
+      </c>
+      <c r="EA15" s="1">
+        <f t="shared" si="29"/>
+        <v>2119.2417193120405</v>
+      </c>
+      <c r="EB15" s="1">
+        <f t="shared" si="29"/>
+        <v>2098.04930211892</v>
+      </c>
+      <c r="EC15" s="1">
+        <f t="shared" si="29"/>
+        <v>2077.0688090977305</v>
+      </c>
+      <c r="ED15" s="1">
+        <f t="shared" si="29"/>
+        <v>2056.2981210067533</v>
+      </c>
+      <c r="EE15" s="1">
+        <f t="shared" si="29"/>
+        <v>2035.7351397966856</v>
+      </c>
+      <c r="EF15" s="1">
+        <f t="shared" si="29"/>
+        <v>2015.3777883987188</v>
+      </c>
+      <c r="EG15" s="1">
+        <f t="shared" si="29"/>
+        <v>1995.2240105147316</v>
+      </c>
+      <c r="EH15" s="1">
+        <f t="shared" si="29"/>
+        <v>1975.2717704095842</v>
+      </c>
+      <c r="EI15" s="1">
+        <f t="shared" si="29"/>
+        <v>1955.5190527054883</v>
+      </c>
+      <c r="EJ15" s="1">
+        <f t="shared" si="29"/>
+        <v>1935.9638621784334</v>
+      </c>
+    </row>
+    <row r="16" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>2</v>
       </c>
+      <c r="C16" s="5">
+        <v>213.7</v>
+      </c>
       <c r="D16" s="5">
         <v>213.7</v>
       </c>
+      <c r="E16" s="5">
+        <v>213.7</v>
+      </c>
+      <c r="F16" s="5">
+        <v>213.7</v>
+      </c>
+      <c r="G16" s="5">
+        <v>213.7</v>
+      </c>
       <c r="H16" s="5">
         <v>213.7</v>
       </c>
+      <c r="I16" s="5">
+        <v>213.7</v>
+      </c>
+      <c r="J16" s="5">
+        <v>213.7</v>
+      </c>
+      <c r="K16" s="5">
+        <v>213.7</v>
+      </c>
       <c r="L16" s="5">
+        <f>312.4</f>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="M16" s="5">
+        <f>312.4</f>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="N16" s="5">
+        <f>312.4</f>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="Q16" s="5">
         <v>213.7</v>
       </c>
-      <c r="M16" s="5">
+      <c r="R16" s="5">
         <v>213.7</v>
       </c>
-      <c r="N16" s="5">
+      <c r="S16" s="5">
         <v>213.7</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T16" s="5">
+        <v>312.8</v>
+      </c>
+      <c r="U16" s="5">
+        <f>312.4</f>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="V16" s="5">
+        <f>312.4</f>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="W16" s="5">
+        <f t="shared" ref="W16:AE16" si="30">312.4</f>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="X16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="Y16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="AA16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="AB16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="AC16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="AD16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.39999999999998</v>
+      </c>
+      <c r="AE16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.39999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>21</v>
       </c>
+      <c r="C17" s="7">
+        <f t="shared" ref="C17:N17" si="31">C15/C16</f>
+        <v>0.50070191857744506</v>
+      </c>
       <c r="D17" s="7">
-        <f>D15/D16</f>
+        <f t="shared" si="31"/>
         <v>3.8792700046794573</v>
       </c>
+      <c r="E17" s="7">
+        <f t="shared" si="31"/>
+        <v>3.2288254562470757</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="31"/>
+        <v>-0.1778193729527375</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="31"/>
+        <v>4.1319606925596633</v>
+      </c>
       <c r="H17" s="7">
-        <f>H15/H16</f>
+        <f t="shared" si="31"/>
         <v>3.7903603182030885</v>
       </c>
+      <c r="I17" s="7">
+        <f t="shared" si="31"/>
+        <v>5.5966307908282644</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="31"/>
+        <v>3.9915769770706602</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="31"/>
+        <v>0.60364997660271413</v>
+      </c>
       <c r="L17" s="7">
-        <f>L15/L16</f>
+        <f t="shared" si="31"/>
+        <v>2.6664532650448147</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" si="31"/>
+        <v>2.1469475032010243</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="31"/>
+        <v>1.8265983226632521</v>
+      </c>
+      <c r="Q17" s="7">
+        <f>Q15/Q16</f>
         <v>1.7641553579784746</v>
       </c>
-      <c r="M17" s="7">
-        <f>M15/M16</f>
+      <c r="R17" s="7">
+        <f>R15/R16</f>
         <v>-0.72063640617688351</v>
       </c>
-      <c r="N17" s="7">
-        <f>N15/N16</f>
+      <c r="S17" s="7">
+        <f>S15/S16</f>
         <v>7.4309780065512401</v>
       </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:V17" si="32">T15/T16</f>
+        <v>11.962915601023017</v>
+      </c>
+      <c r="U17" s="7">
+        <f t="shared" si="32"/>
+        <v>7.0529312291933444</v>
+      </c>
+      <c r="V17" s="7">
+        <f t="shared" si="32"/>
+        <v>12.455317351959023</v>
+      </c>
+      <c r="W17" s="7">
+        <f t="shared" ref="W17:AE17" si="33">W15/W16</f>
+        <v>13.546740592036359</v>
+      </c>
+      <c r="X17" s="7">
+        <f t="shared" si="33"/>
+        <v>14.428079192158416</v>
+      </c>
+      <c r="Y17" s="7">
+        <f t="shared" si="33"/>
+        <v>15.204858756763027</v>
+      </c>
+      <c r="Z17" s="7">
+        <f t="shared" si="33"/>
+        <v>15.855000127818553</v>
+      </c>
+      <c r="AA17" s="7">
+        <f t="shared" si="33"/>
+        <v>16.35889445898168</v>
+      </c>
+      <c r="AB17" s="7">
+        <f t="shared" si="33"/>
+        <v>16.878188063352979</v>
+      </c>
+      <c r="AC17" s="7">
+        <f t="shared" si="33"/>
+        <v>17.413345743561443</v>
+      </c>
+      <c r="AD17" s="7">
+        <f t="shared" si="33"/>
+        <v>17.964846274559232</v>
+      </c>
+      <c r="AE17" s="7">
+        <f t="shared" si="33"/>
+        <v>18.533182823073862</v>
+      </c>
+    </row>
+    <row r="19" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>33</v>
       </c>
+      <c r="C19" s="9"/>
       <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9">
+        <f t="shared" ref="G19:L19" si="34">G3/C3-1</f>
+        <v>-0.18559153998678124</v>
+      </c>
       <c r="H19" s="9">
-        <f>H3/D3-1</f>
+        <f t="shared" si="34"/>
         <v>5.3250091810503886E-3</v>
       </c>
+      <c r="I19" s="9">
+        <f t="shared" si="34"/>
+        <v>7.1837669775814073E-2</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="34"/>
+        <v>-7.1428571428571397E-2</v>
+      </c>
+      <c r="K19" s="9">
+        <f t="shared" si="34"/>
+        <v>0.10176919331277401</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="34"/>
+        <v>0.11433789954337903</v>
+      </c>
       <c r="M19" s="9">
-        <f>M3/L3-1</f>
+        <f t="shared" ref="M19:N19" si="35">M3/I3-1</f>
+        <v>6.8702290076335881E-2</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" si="35"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="R19" s="9">
+        <f>R3/Q3-1</f>
         <v>0.24382920250394413</v>
       </c>
-      <c r="N19" s="9">
-        <f>N3/M3-1</f>
+      <c r="S19" s="9">
+        <f>S3/R3-1</f>
         <v>1.9558101472995082E-2</v>
       </c>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="T19" s="9">
+        <f t="shared" ref="T19:AE19" si="36">T3/S3-1</f>
+        <v>-5.4177702865398469E-2</v>
+      </c>
+      <c r="U19" s="9">
+        <f t="shared" si="36"/>
+        <v>9.5095044127630812E-2</v>
+      </c>
+      <c r="V19" s="9">
+        <f t="shared" si="36"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="W19" s="9">
+        <f t="shared" si="36"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" si="36"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="Y19" s="9">
+        <f t="shared" si="36"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="Z19" s="9">
+        <f t="shared" si="36"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AA19" s="9">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AB19" s="9">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC19" s="9">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD19" s="9">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE19" s="9">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="9">
+        <f t="shared" ref="C20:K20" si="37">(C3-C4)/C3</f>
+        <v>0.24269662921348314</v>
+      </c>
+      <c r="D20" s="9">
+        <f t="shared" si="37"/>
+        <v>0.46988615497612929</v>
+      </c>
+      <c r="E20" s="9">
+        <f t="shared" si="37"/>
+        <v>0.44902634593356244</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="37"/>
+        <v>0.30676328502415456</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="37"/>
+        <v>0.44538224314234703</v>
+      </c>
+      <c r="H20" s="9">
+        <f t="shared" si="37"/>
+        <v>0.58136986301369864</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="37"/>
+        <v>0.52381679389312974</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="37"/>
+        <v>0.51858045336306202</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="37"/>
+        <v>0.3541543901001768</v>
+      </c>
+      <c r="L20" s="9">
+        <f>(L3-L4)/L3</f>
+        <v>0.48664153417472544</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" ref="M20:N20" si="38">(M3-M4)/M3</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" si="38"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="Q20" s="9">
+        <f t="shared" ref="Q20:T20" si="39">(Q3-Q4)/Q3</f>
+        <v>0.38098630973586445</v>
+      </c>
+      <c r="R20" s="9">
+        <f t="shared" si="39"/>
+        <v>0.28551554828150572</v>
+      </c>
+      <c r="S20" s="9">
+        <f t="shared" si="39"/>
+        <v>0.35785376033389515</v>
+      </c>
+      <c r="T20" s="9">
+        <f t="shared" si="39"/>
+        <v>0.51548710115410723</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" ref="U20:AE20" si="40">(U3-U4)/U3</f>
+        <v>0.43345357469429507</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43999999999999989</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43999999999999989</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43999999999999989</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.44</v>
+      </c>
+      <c r="AA20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AB20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.44</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH20" s="9">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="21" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="9">
+        <f t="shared" ref="C21:K21" si="41">(C3-C5)/C3</f>
+        <v>0.81070720423000664</v>
+      </c>
+      <c r="D21" s="9">
+        <f t="shared" si="41"/>
+        <v>0.72879177377892035</v>
+      </c>
+      <c r="E21" s="9">
+        <f t="shared" si="41"/>
+        <v>0.77859597447226314</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="41"/>
+        <v>0.75448585231193932</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="41"/>
+        <v>0.75880538873559489</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="41"/>
+        <v>0.69954337899543384</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="41"/>
+        <v>0.7656488549618321</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="41"/>
+        <v>0.72259383128948351</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="41"/>
+        <v>0.77239245727754857</v>
+      </c>
+      <c r="L21" s="9">
+        <f>(L3-L5)/L3</f>
+        <v>0.73496148172430753</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" ref="M21:N21" si="42">(M3-M5)/M3</f>
+        <v>0.75</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" si="42"/>
+        <v>0.75</v>
+      </c>
+      <c r="Q21" s="9">
+        <f t="shared" ref="Q21:T21" si="43">(Q3-Q5)/Q3</f>
+        <v>0.76818158684920357</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" si="43"/>
+        <v>0.80192307692307696</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" si="43"/>
+        <v>0.77185167348904404</v>
+      </c>
+      <c r="T21" s="9">
+        <f t="shared" si="43"/>
+        <v>0.7386710794297352</v>
+      </c>
+      <c r="U21" s="9">
+        <f t="shared" ref="U21:AE21" si="44">(U3-U5)/U3</f>
+        <v>0.75233443888225904</v>
+      </c>
+      <c r="V21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.76999999999999991</v>
+      </c>
+      <c r="W21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.77</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.77</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.77</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.76999999999999991</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.77</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.77</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.77</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.77</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.77</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH21" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="9">
-        <f>D7/D3</f>
+      <c r="C22" s="9">
+        <f t="shared" ref="C22:L22" si="45">C7/C3</f>
+        <v>5.3403833443489757E-2</v>
+      </c>
+      <c r="D22" s="9">
+        <f t="shared" si="45"/>
         <v>0.19867792875504958</v>
       </c>
-      <c r="H20" s="9">
-        <f>H7/H3</f>
+      <c r="E22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.22762232040582556</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" si="45"/>
+        <v>6.1249137336093856E-2</v>
+      </c>
+      <c r="G22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.20418763187794189</v>
+      </c>
+      <c r="H22" s="9">
+        <f t="shared" si="45"/>
         <v>0.28091324200913242</v>
       </c>
-      <c r="L20" s="9">
-        <f>L7/L3</f>
+      <c r="I22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.28946564885496184</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.24117428465254553</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.1265468473777254</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="45"/>
+        <v>0.22160301589903295</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" ref="M22:N22" si="46">M7/M3</f>
+        <v>0.2</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="46"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="Q22" s="9">
+        <f>Q7/Q3</f>
         <v>0.14916789658506793</v>
       </c>
-      <c r="M20" s="9">
-        <f>M7/M3</f>
+      <c r="R22" s="9">
+        <f>R7/R3</f>
         <v>8.7438625204582648E-2</v>
       </c>
-      <c r="N20" s="9">
-        <f>N7/N3</f>
+      <c r="S22" s="9">
+        <f>S7/S3</f>
         <v>0.12970543382293925</v>
       </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+      <c r="T22" s="9">
+        <f t="shared" ref="T22:AE22" si="47">T7/T3</f>
+        <v>0.25415818058384249</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.18578801357655411</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.20999999999999991</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.20999999999999991</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.20999999999999991</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.20999999999999985</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.20999999999999994</v>
+      </c>
+      <c r="AA22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.21</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.21</v>
+      </c>
+      <c r="AC22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.20999999999999996</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.20999999999999994</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH22" s="5">
+        <f>NPV(AH21,U15:EJ15)</f>
+        <v>67884.566725731507</v>
+      </c>
+    </row>
+    <row r="23" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="9">
-        <f>D10/D3</f>
+      <c r="C23" s="9">
+        <f t="shared" ref="C23:L23" si="48">C10/C3</f>
+        <v>6.6093853271645734E-4</v>
+      </c>
+      <c r="D23" s="9">
+        <f t="shared" si="48"/>
         <v>0.12284245317664341</v>
       </c>
-      <c r="H21" s="9">
-        <f>H10/H3</f>
+      <c r="E23" s="9">
+        <f t="shared" si="48"/>
+        <v>0.15987563410243821</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="48"/>
+        <v>-1.1732229123533472E-2</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="48"/>
+        <v>0.13195909754909918</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="48"/>
         <v>0.20091324200913241</v>
       </c>
-      <c r="L21" s="9">
-        <f>L10/L3</f>
+      <c r="I23" s="9">
+        <f t="shared" si="48"/>
+        <v>0.22366412213740458</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="48"/>
+        <v>0.1677814938684504</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="48"/>
+        <v>6.6440777843252793E-2</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="48"/>
+        <v>0.15587608588755941</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" ref="M23:N23" si="49">M10/M3</f>
+        <v>0.13686000000000001</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="49"/>
+        <v>0.13163494476537951</v>
+      </c>
+      <c r="Q23" s="9">
+        <f>Q10/Q3</f>
         <v>-2.7838566848185659E-2</v>
       </c>
-      <c r="M21" s="9">
-        <f>M10/M3</f>
+      <c r="R23" s="9">
+        <f>R10/R3</f>
         <v>2.021276595744681E-2</v>
       </c>
-      <c r="N21" s="9">
-        <f>N10/N3</f>
+      <c r="S23" s="9">
+        <f>S10/S3</f>
         <v>6.3528373063648766E-2</v>
       </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="T23" s="9">
+        <f t="shared" ref="T23:AE23" si="50">T10/T3</f>
+        <v>0.18164460285132383</v>
+      </c>
+      <c r="U23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.12163589727694003</v>
+      </c>
+      <c r="V23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999994</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999991</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999991</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999988</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999994</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999999</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999999</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18480000000000002</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999996</v>
+      </c>
+      <c r="AE23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.18479999999999994</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH23" s="5">
+        <f>Main!D8</f>
+        <v>-6249</v>
+      </c>
+    </row>
+    <row r="24" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="9">
-        <f>D14/D13</f>
+      <c r="C24" s="9">
+        <f t="shared" ref="C24:L24" si="51">C14/C13</f>
+        <v>0.55042016806722693</v>
+      </c>
+      <c r="D24" s="9">
+        <f t="shared" si="51"/>
         <v>0.29205807002561912</v>
       </c>
-      <c r="H22" s="9">
-        <f>H14/H13</f>
+      <c r="E24" s="9">
+        <f t="shared" si="51"/>
+        <v>0.22905027932960895</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="51"/>
+        <v>1.2657342657342658</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="51"/>
+        <v>0.15744274809160305</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="51"/>
         <v>0.15975103734439833</v>
       </c>
-      <c r="L22" s="9">
-        <f>L14/L13</f>
+      <c r="I24" s="9">
+        <f t="shared" si="51"/>
+        <v>0.27294832826747722</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="51"/>
+        <v>6.9848661233993014E-3</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="51"/>
+        <v>0.14569536423841059</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="51"/>
+        <v>0.34564021995286726</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" ref="M24:N24" si="52">M14/M13</f>
+        <v>0.17000000000000004</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="52"/>
+        <v>0.17</v>
+      </c>
+      <c r="Q24" s="9">
+        <f>Q14/Q13</f>
         <v>-1.4802631578947369</v>
       </c>
-      <c r="M22" s="9">
-        <f>M14/M13</f>
+      <c r="R24" s="9">
+        <f>R14/R13</f>
         <v>0.71586715867158668</v>
       </c>
-      <c r="N22" s="9">
-        <f>N14/N13</f>
+      <c r="S24" s="9">
+        <f>S14/S13</f>
         <v>0.35104209235798939</v>
       </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+      <c r="T24" s="9">
+        <f t="shared" ref="T24:AE24" si="53">T14/T13</f>
+        <v>0.17139061116031887</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.24532576887977098</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH24" s="5">
+        <f>AH22+AH23</f>
+        <v>61635.566725731507</v>
+      </c>
+    </row>
+    <row r="25" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="9">
-        <f>D15/D3</f>
+      <c r="C25" s="9">
+        <f t="shared" ref="C25:L25" si="54">C15/C3</f>
+        <v>1.4144084600132188E-2</v>
+      </c>
+      <c r="D25" s="9">
+        <f t="shared" si="54"/>
         <v>0.15222181417554168</v>
       </c>
-      <c r="H23" s="9">
-        <f>H15/H3</f>
+      <c r="E25" s="9">
+        <f t="shared" si="54"/>
+        <v>0.11291114383897889</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="54"/>
+        <v>-6.556245686680469E-3</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="54"/>
+        <v>0.14332088946599578</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="54"/>
         <v>0.14794520547945206</v>
       </c>
-      <c r="L23" s="9">
-        <f>L15/L3</f>
+      <c r="I25" s="9">
+        <f t="shared" si="54"/>
+        <v>0.18259541984732824</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="54"/>
+        <v>0.15849126718691936</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="54"/>
+        <v>1.9004124926340602E-2</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="54"/>
+        <v>0.13653499426323554</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" ref="M25:N25" si="55">M15/M3</f>
+        <v>9.5815199999999989E-2</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="55"/>
+        <v>9.638683085030908E-2</v>
+      </c>
+      <c r="Q25" s="9">
+        <f>Q15/Q3</f>
         <v>1.9186727059901269E-2</v>
       </c>
-      <c r="M23" s="9">
-        <f>M15/M3</f>
+      <c r="R25" s="9">
+        <f>R15/R3</f>
         <v>-6.3011456628477907E-3</v>
       </c>
-      <c r="N23" s="9">
-        <f>N15/N3</f>
+      <c r="S25" s="9">
+        <f>S15/S3</f>
         <v>6.3729031222409499E-2</v>
+      </c>
+      <c r="T25" s="9">
+        <f t="shared" ref="T25:AE25" si="56">T15/T3</f>
+        <v>0.15877460964019008</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="56"/>
+        <v>8.5370167072206821E-2</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.13831356704010098</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.13929035436157591</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.13995514896716196</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.14046672424460335</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.14083933796831677</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.14108292363883496</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.14132177949050806</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.1415559973644788</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.14178566731856657</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.14201087766189532</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH25" s="6">
+        <f>AH24/AE16</f>
+        <v>197.29694854587552</v>
+      </c>
+    </row>
+    <row r="26" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="AG26" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH26" s="6">
+        <f>Main!D3</f>
+        <v>332.45</v>
+      </c>
+    </row>
+    <row r="27" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="AG27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH27" s="10">
+        <f>AH25/AH26-1</f>
+        <v>-0.40653647602383658</v>
+      </c>
+    </row>
+    <row r="28" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH28" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L42" s="8">
+        <v>53038</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Financial Analysis/CEG.xlsx
+++ b/Financial Analysis/CEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AEA03C-D25E-42C2-88CB-76A3DDD8BFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C612F77C-918A-4F45-A32B-D54D76B83268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FD8B9579-E08E-4C89-8726-3FC953CC4FC9}"/>
   </bookViews>
@@ -746,14 +746,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>332.45</v>
+        <v>384.26</v>
       </c>
       <c r="E3" s="4">
-        <v>45909</v>
+        <v>45950</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45927</v>
+        <v>45950</v>
       </c>
       <c r="G3" s="4">
         <v>45971</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>103857.37999999999</v>
+        <v>120042.82399999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>110106.37999999999</v>
+        <v>126291.82399999999</v>
       </c>
     </row>
   </sheetData>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AH26" s="6">
         <f>Main!D3</f>
-        <v>332.45</v>
+        <v>384.26</v>
       </c>
     </row>
     <row r="27" spans="2:34" x14ac:dyDescent="0.3">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AH27" s="10">
         <f>AH25/AH26-1</f>
-        <v>-0.40653647602383658</v>
+        <v>-0.48655350922324592</v>
       </c>
     </row>
     <row r="28" spans="2:34" x14ac:dyDescent="0.3">

--- a/Financial Analysis/CEG.xlsx
+++ b/Financial Analysis/CEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C612F77C-918A-4F45-A32B-D54D76B83268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2155018A-1360-40D3-940B-C489A21A48B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FD8B9579-E08E-4C89-8726-3FC953CC4FC9}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
   <si>
     <t>CEG</t>
   </si>
@@ -224,6 +224,18 @@
   </si>
   <si>
     <t>Total assets</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -323,13 +335,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
@@ -373,14 +385,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
@@ -397,8 +409,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8031480" y="15240"/>
-          <a:ext cx="0" cy="6065520"/>
+          <a:off x="9258300" y="15240"/>
+          <a:ext cx="0" cy="6431280"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -746,17 +758,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>384.26</v>
+        <v>312.64</v>
       </c>
       <c r="E3" s="4">
-        <v>45950</v>
+        <v>46078</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45950</v>
+        <v>46078</v>
       </c>
       <c r="G3" s="4">
-        <v>45971</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -764,11 +776,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>312.4</f>
-        <v>312.39999999999998</v>
+        <f>312.3</f>
+        <v>312.3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -777,7 +789,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>120042.82399999999</v>
+        <v>97637.471999999994</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -785,11 +797,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>1974+88</f>
-        <v>2062</v>
+        <f>3641+107</f>
+        <v>3748</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -797,11 +809,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>900+125+7286</f>
-        <v>8311</v>
+        <f>1650+92+7250</f>
+        <v>8992</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -810,7 +822,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-6249</v>
+        <v>-5244</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +831,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>126291.82399999999</v>
+        <v>102881.47199999999</v>
       </c>
     </row>
   </sheetData>
@@ -829,14 +841,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4841C5-2D92-4E0E-A023-57C39442136D}">
-  <dimension ref="B2:EJ42"/>
+  <dimension ref="B2:EM42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:140" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:143" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
@@ -873,54 +885,65 @@
       <c r="N2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="Q2">
+      <c r="O2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2">
         <v>2021</v>
       </c>
-      <c r="R2">
+      <c r="U2">
         <v>2022</v>
       </c>
-      <c r="S2">
+      <c r="V2">
         <v>2023</v>
       </c>
-      <c r="T2">
+      <c r="W2">
         <v>2024</v>
       </c>
-      <c r="U2">
+      <c r="X2">
         <v>2025</v>
       </c>
-      <c r="V2">
+      <c r="Y2">
         <v>2026</v>
       </c>
-      <c r="W2">
+      <c r="Z2">
         <v>2027</v>
       </c>
-      <c r="X2">
+      <c r="AA2">
         <v>2028</v>
       </c>
-      <c r="Y2">
+      <c r="AB2">
         <v>2029</v>
       </c>
-      <c r="Z2">
+      <c r="AC2">
         <v>2030</v>
       </c>
-      <c r="AA2">
+      <c r="AD2">
         <v>2031</v>
       </c>
-      <c r="AB2">
+      <c r="AE2">
         <v>2032</v>
       </c>
-      <c r="AC2">
+      <c r="AF2">
         <v>2033</v>
       </c>
-      <c r="AD2">
+      <c r="AG2">
         <v>2034</v>
       </c>
-      <c r="AE2">
+      <c r="AH2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -934,7 +957,7 @@
         <v>6111</v>
       </c>
       <c r="F3" s="8">
-        <f>S3-E3-D3-C3</f>
+        <f>V3-E3-D3-C3</f>
         <v>5796</v>
       </c>
       <c r="G3" s="8">
@@ -947,7 +970,7 @@
         <v>6550</v>
       </c>
       <c r="J3" s="8">
-        <f>T3-I3-H3-G3</f>
+        <f>W3-I3-H3-G3</f>
         <v>5382</v>
       </c>
       <c r="K3" s="8">
@@ -957,71 +980,73 @@
         <v>6101</v>
       </c>
       <c r="M3" s="8">
-        <v>7000</v>
+        <v>6570</v>
       </c>
       <c r="N3" s="8">
-        <f>J3*1.1</f>
-        <v>5920.2000000000007</v>
-      </c>
-      <c r="Q3" s="8">
+        <v>6074</v>
+      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="T3" s="8">
         <v>19649</v>
       </c>
-      <c r="R3" s="8">
+      <c r="U3" s="8">
         <f>24280+160</f>
         <v>24440</v>
       </c>
-      <c r="S3" s="8">
+      <c r="V3" s="8">
         <v>24918</v>
       </c>
-      <c r="T3" s="8">
+      <c r="W3" s="8">
         <v>23568</v>
       </c>
-      <c r="U3" s="8">
+      <c r="X3" s="8">
         <f>SUM(K3:N3)</f>
-        <v>25809.200000000001</v>
-      </c>
-      <c r="V3" s="8">
-        <f>U3*1.09</f>
-        <v>28132.028000000002</v>
-      </c>
-      <c r="W3" s="8">
-        <f>V3*1.08</f>
-        <v>30382.590240000005</v>
-      </c>
-      <c r="X3" s="8">
-        <f>W3*1.06</f>
-        <v>32205.545654400008</v>
+        <v>25533</v>
       </c>
       <c r="Y3" s="8">
-        <f>X3*1.05</f>
-        <v>33815.822937120007</v>
+        <f>X3*1.1</f>
+        <v>28086.300000000003</v>
       </c>
       <c r="Z3" s="8">
-        <f>Y3*1.04</f>
-        <v>35168.455854604807</v>
+        <f>Y3*1.08</f>
+        <v>30333.204000000005</v>
       </c>
       <c r="AA3" s="8">
-        <f t="shared" ref="AA3:AE3" si="0">Z3*1.03</f>
-        <v>36223.509530242954</v>
+        <f>Z3*1.06</f>
+        <v>32153.196240000008</v>
       </c>
       <c r="AB3" s="8">
-        <f t="shared" si="0"/>
-        <v>37310.214816150241</v>
+        <f>AA3*1.05</f>
+        <v>33760.85605200001</v>
       </c>
       <c r="AC3" s="8">
-        <f t="shared" si="0"/>
-        <v>38429.521260634749</v>
+        <f>AB3*1.04</f>
+        <v>35111.290294080012</v>
       </c>
       <c r="AD3" s="8">
-        <f t="shared" si="0"/>
-        <v>39582.406898453795</v>
+        <f t="shared" ref="AD3:AH3" si="0">AC3*1.03</f>
+        <v>36164.629002902417</v>
       </c>
       <c r="AE3" s="8">
         <f t="shared" si="0"/>
-        <v>40769.87910540741</v>
-      </c>
-    </row>
-    <row r="4" spans="2:140" x14ac:dyDescent="0.3">
+        <v>37249.567872989493</v>
+      </c>
+      <c r="AF3" s="8">
+        <f t="shared" si="0"/>
+        <v>38367.054909179176</v>
+      </c>
+      <c r="AG3" s="8">
+        <f t="shared" si="0"/>
+        <v>39518.066556454556</v>
+      </c>
+      <c r="AH3" s="8">
+        <f t="shared" si="0"/>
+        <v>40703.608553148195</v>
+      </c>
+    </row>
+    <row r="4" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -1035,7 +1060,7 @@
         <v>3367</v>
       </c>
       <c r="F4" s="5">
-        <f>S4-E4-D4-C4</f>
+        <f>V4-E4-D4-C4</f>
         <v>4018</v>
       </c>
       <c r="G4" s="5">
@@ -1048,7 +1073,7 @@
         <v>3119</v>
       </c>
       <c r="J4" s="5">
-        <f>T4-I4-H4-G4</f>
+        <f>W4-I4-H4-G4</f>
         <v>2591</v>
       </c>
       <c r="K4" s="5">
@@ -1058,73 +1083,74 @@
         <v>3132</v>
       </c>
       <c r="M4" s="5">
-        <f>M3*0.55</f>
-        <v>3850.0000000000005</v>
+        <v>3567</v>
       </c>
       <c r="N4" s="5">
-        <f>N3*0.55</f>
-        <v>3256.1100000000006</v>
-      </c>
-      <c r="Q4" s="5">
+        <v>3598</v>
+      </c>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="T4" s="5">
         <f>12157+6</f>
         <v>12163</v>
       </c>
-      <c r="R4" s="5">
+      <c r="U4" s="5">
         <f>17457+5</f>
         <v>17462</v>
       </c>
-      <c r="S4" s="5">
+      <c r="V4" s="5">
         <v>16001</v>
       </c>
-      <c r="T4" s="5">
+      <c r="W4" s="5">
         <v>11419</v>
       </c>
-      <c r="U4" s="5">
+      <c r="X4" s="5">
         <f>SUM(K4:N4)</f>
-        <v>14622.11</v>
-      </c>
-      <c r="V4" s="5">
-        <f>V3*0.56</f>
-        <v>15753.935680000002</v>
-      </c>
-      <c r="W4" s="5">
-        <f t="shared" ref="W4:AE4" si="1">W3*0.56</f>
-        <v>17014.250534400006</v>
-      </c>
-      <c r="X4" s="5">
-        <f t="shared" si="1"/>
-        <v>18035.105566464008</v>
+        <v>14681</v>
       </c>
       <c r="Y4" s="5">
-        <f t="shared" si="1"/>
-        <v>18936.860844787207</v>
+        <f>Y3*0.57</f>
+        <v>16009.191000000001</v>
       </c>
       <c r="Z4" s="5">
-        <f t="shared" si="1"/>
-        <v>19694.335278578692</v>
+        <f t="shared" ref="Z4:AH4" si="1">Z3*0.57</f>
+        <v>17289.92628</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" si="1"/>
-        <v>20285.165336936057</v>
+        <v>18327.321856800005</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="1"/>
-        <v>20893.720297044136</v>
+        <v>19243.687949640003</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" si="1"/>
-        <v>21520.53190595546</v>
+        <v>20013.435467625604</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="1"/>
-        <v>22166.147863134127</v>
+        <v>20613.838531654375</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="1"/>
-        <v>22831.132299028151</v>
-      </c>
-    </row>
-    <row r="5" spans="2:140" x14ac:dyDescent="0.3">
+        <v>21232.25368760401</v>
+      </c>
+      <c r="AF4" s="5">
+        <f t="shared" si="1"/>
+        <v>21869.221298232129</v>
+      </c>
+      <c r="AG4" s="5">
+        <f t="shared" si="1"/>
+        <v>22525.297937179093</v>
+      </c>
+      <c r="AH4" s="5">
+        <f t="shared" si="1"/>
+        <v>23201.056875294467</v>
+      </c>
+    </row>
+    <row r="5" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -1138,7 +1164,7 @@
         <v>1353</v>
       </c>
       <c r="F5" s="5">
-        <f>S5-E5-D5-C5</f>
+        <f>V5-E5-D5-C5</f>
         <v>1423</v>
       </c>
       <c r="G5" s="5">
@@ -1151,7 +1177,7 @@
         <v>1535</v>
       </c>
       <c r="J5" s="5">
-        <f>T5-I5-H5-G5</f>
+        <f>W5-I5-H5-G5</f>
         <v>1493</v>
       </c>
       <c r="K5" s="5">
@@ -1161,73 +1187,74 @@
         <v>1617</v>
       </c>
       <c r="M5" s="5">
-        <f>M3*0.25</f>
-        <v>1750</v>
+        <v>1511</v>
       </c>
       <c r="N5" s="5">
-        <f>N3*0.25</f>
-        <v>1480.0500000000002</v>
-      </c>
-      <c r="Q5" s="5">
+        <v>1486</v>
+      </c>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="T5" s="5">
         <f>3934+621</f>
         <v>4555</v>
       </c>
-      <c r="R5" s="5">
+      <c r="U5" s="5">
         <f>4797+44</f>
         <v>4841</v>
       </c>
-      <c r="S5" s="5">
+      <c r="V5" s="5">
         <v>5685</v>
       </c>
-      <c r="T5" s="5">
+      <c r="W5" s="5">
         <v>6159</v>
       </c>
-      <c r="U5" s="5">
+      <c r="X5" s="5">
         <f>SUM(K5:N5)</f>
-        <v>6392.05</v>
-      </c>
-      <c r="V5" s="5">
-        <f>V3*0.23</f>
-        <v>6470.3664400000007</v>
-      </c>
-      <c r="W5" s="5">
-        <f t="shared" ref="W5:AE5" si="2">W3*0.23</f>
-        <v>6987.9957552000014</v>
-      </c>
-      <c r="X5" s="5">
-        <f t="shared" si="2"/>
-        <v>7407.2755005120025</v>
+        <v>6159</v>
       </c>
       <c r="Y5" s="5">
-        <f t="shared" si="2"/>
-        <v>7777.6392755376019</v>
+        <f>Y3*0.24</f>
+        <v>6740.7120000000004</v>
       </c>
       <c r="Z5" s="5">
-        <f t="shared" si="2"/>
-        <v>8088.744846559106</v>
+        <f t="shared" ref="Z5:AH5" si="2">Z3*0.24</f>
+        <v>7279.9689600000011</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" si="2"/>
-        <v>8331.4071919558792</v>
+        <v>7716.7670976000018</v>
       </c>
       <c r="AB5" s="5">
         <f t="shared" si="2"/>
-        <v>8581.3494077145551</v>
+        <v>8102.605452480002</v>
       </c>
       <c r="AC5" s="5">
         <f t="shared" si="2"/>
-        <v>8838.7898899459924</v>
+        <v>8426.7096705792028</v>
       </c>
       <c r="AD5" s="5">
         <f t="shared" si="2"/>
-        <v>9103.953586644373</v>
+        <v>8679.5109606965798</v>
       </c>
       <c r="AE5" s="5">
         <f t="shared" si="2"/>
-        <v>9377.0721942437049</v>
-      </c>
-    </row>
-    <row r="6" spans="2:140" x14ac:dyDescent="0.3">
+        <v>8939.8962895174773</v>
+      </c>
+      <c r="AF5" s="5">
+        <f t="shared" si="2"/>
+        <v>9208.093178203002</v>
+      </c>
+      <c r="AG5" s="5">
+        <f t="shared" si="2"/>
+        <v>9484.335973549094</v>
+      </c>
+      <c r="AH5" s="5">
+        <f t="shared" si="2"/>
+        <v>9768.8660527555658</v>
+      </c>
+    </row>
+    <row r="6" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>32</v>
       </c>
@@ -1273,74 +1300,77 @@
       </c>
       <c r="M6" s="5">
         <f t="shared" ref="M6:N6" si="4">M4+M5</f>
-        <v>5600</v>
+        <v>5078</v>
       </c>
       <c r="N6" s="5">
         <f t="shared" si="4"/>
-        <v>4736.1600000000008</v>
-      </c>
-      <c r="Q6" s="5">
-        <f t="shared" ref="Q6:V6" si="5">Q4+Q5</f>
+        <v>5084</v>
+      </c>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="T6" s="5">
+        <f t="shared" ref="T6:Y6" si="5">T4+T5</f>
         <v>16718</v>
       </c>
-      <c r="R6" s="5">
+      <c r="U6" s="5">
         <f t="shared" si="5"/>
         <v>22303</v>
       </c>
-      <c r="S6" s="5">
+      <c r="V6" s="5">
         <f t="shared" si="5"/>
         <v>21686</v>
       </c>
-      <c r="T6" s="5">
+      <c r="W6" s="5">
         <f t="shared" si="5"/>
         <v>17578</v>
       </c>
-      <c r="U6" s="5">
+      <c r="X6" s="5">
         <f t="shared" si="5"/>
-        <v>21014.16</v>
-      </c>
-      <c r="V6" s="5">
+        <v>20840</v>
+      </c>
+      <c r="Y6" s="5">
         <f t="shared" si="5"/>
-        <v>22224.302120000004</v>
-      </c>
-      <c r="W6" s="5">
-        <f t="shared" ref="W6:AE6" si="6">W4+W5</f>
-        <v>24002.246289600007</v>
-      </c>
-      <c r="X6" s="5">
-        <f t="shared" si="6"/>
-        <v>25442.38106697601</v>
-      </c>
-      <c r="Y6" s="5">
-        <f t="shared" si="6"/>
-        <v>26714.50012032481</v>
+        <v>22749.903000000002</v>
       </c>
       <c r="Z6" s="5">
-        <f t="shared" si="6"/>
-        <v>27783.0801251378</v>
+        <f t="shared" ref="Z6:AH6" si="6">Z4+Z5</f>
+        <v>24569.895240000002</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" si="6"/>
-        <v>28616.572528891935</v>
+        <v>26044.088954400006</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="6"/>
-        <v>29475.069704758691</v>
+        <v>27346.293402120005</v>
       </c>
       <c r="AC6" s="5">
         <f t="shared" si="6"/>
-        <v>30359.321795901451</v>
+        <v>28440.145138204807</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="6"/>
-        <v>31270.1014497785</v>
+        <v>29293.349492350957</v>
       </c>
       <c r="AE6" s="5">
         <f t="shared" si="6"/>
-        <v>32208.204493271856</v>
-      </c>
-    </row>
-    <row r="7" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>30172.149977121488</v>
+      </c>
+      <c r="AF6" s="5">
+        <f t="shared" si="6"/>
+        <v>31077.314476435131</v>
+      </c>
+      <c r="AG6" s="5">
+        <f t="shared" si="6"/>
+        <v>32009.633910728189</v>
+      </c>
+      <c r="AH6" s="5">
+        <f t="shared" si="6"/>
+        <v>32969.922928050029</v>
+      </c>
+    </row>
+    <row r="7" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
@@ -1386,74 +1416,77 @@
       </c>
       <c r="M7" s="8">
         <f t="shared" ref="M7:N7" si="8">M3-M6</f>
-        <v>1400</v>
+        <v>1492</v>
       </c>
       <c r="N7" s="8">
         <f t="shared" si="8"/>
-        <v>1184.04</v>
-      </c>
-      <c r="Q7" s="8">
-        <f t="shared" ref="Q7:V7" si="9">Q3-Q6</f>
+        <v>990</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="T7" s="8">
+        <f t="shared" ref="T7:Y7" si="9">T3-T6</f>
         <v>2931</v>
       </c>
-      <c r="R7" s="8">
+      <c r="U7" s="8">
         <f t="shared" si="9"/>
         <v>2137</v>
       </c>
-      <c r="S7" s="8">
+      <c r="V7" s="8">
         <f t="shared" si="9"/>
         <v>3232</v>
       </c>
-      <c r="T7" s="8">
+      <c r="W7" s="8">
         <f t="shared" si="9"/>
         <v>5990</v>
       </c>
-      <c r="U7" s="8">
+      <c r="X7" s="8">
         <f t="shared" si="9"/>
-        <v>4795.0400000000009</v>
-      </c>
-      <c r="V7" s="8">
+        <v>4693</v>
+      </c>
+      <c r="Y7" s="8">
         <f t="shared" si="9"/>
-        <v>5907.7258799999981</v>
-      </c>
-      <c r="W7" s="8">
-        <f t="shared" ref="W7:AE7" si="10">W3-W6</f>
-        <v>6380.343950399998</v>
-      </c>
-      <c r="X7" s="8">
-        <f t="shared" si="10"/>
-        <v>6763.1645874239985</v>
-      </c>
-      <c r="Y7" s="8">
-        <f t="shared" si="10"/>
-        <v>7101.3228167951966</v>
+        <v>5336.3970000000008</v>
       </c>
       <c r="Z7" s="8">
-        <f t="shared" si="10"/>
-        <v>7385.3757294670067</v>
+        <f t="shared" ref="Z7:AH7" si="10">Z3-Z6</f>
+        <v>5763.3087600000035</v>
       </c>
       <c r="AA7" s="8">
         <f t="shared" si="10"/>
-        <v>7606.9370013510197</v>
+        <v>6109.1072856000028</v>
       </c>
       <c r="AB7" s="8">
         <f t="shared" si="10"/>
-        <v>7835.14511139155</v>
+        <v>6414.5626498800048</v>
       </c>
       <c r="AC7" s="8">
         <f t="shared" si="10"/>
-        <v>8070.1994647332976</v>
+        <v>6671.1451558752051</v>
       </c>
       <c r="AD7" s="8">
         <f t="shared" si="10"/>
-        <v>8312.3054486752953</v>
+        <v>6871.2795105514597</v>
       </c>
       <c r="AE7" s="8">
         <f t="shared" si="10"/>
-        <v>8561.6746121355536</v>
-      </c>
-    </row>
-    <row r="8" spans="2:140" x14ac:dyDescent="0.3">
+        <v>7077.4178958680059</v>
+      </c>
+      <c r="AF7" s="8">
+        <f t="shared" si="10"/>
+        <v>7289.7404327440454</v>
+      </c>
+      <c r="AG7" s="8">
+        <f t="shared" si="10"/>
+        <v>7508.4326457263669</v>
+      </c>
+      <c r="AH7" s="8">
+        <f t="shared" si="10"/>
+        <v>7733.6856250981655</v>
+      </c>
+    </row>
+    <row r="8" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -1467,7 +1500,7 @@
         <v>266</v>
       </c>
       <c r="F8" s="5">
-        <f t="shared" ref="F8:F9" si="11">S8-E8-D8-C8</f>
+        <f t="shared" ref="F8:F9" si="11">V8-E8-D8-C8</f>
         <v>289</v>
       </c>
       <c r="G8" s="5">
@@ -1480,7 +1513,7 @@
         <v>266</v>
       </c>
       <c r="J8" s="5">
-        <f>T8-I8-H8-G8</f>
+        <f>W8-I8-H8-G8</f>
         <v>255</v>
       </c>
       <c r="K8" s="5">
@@ -1490,37 +1523,29 @@
         <v>254</v>
       </c>
       <c r="M8" s="5">
-        <f>I8*1.03</f>
-        <v>273.98</v>
+        <v>241</v>
       </c>
       <c r="N8" s="5">
-        <f>J8*1.03</f>
-        <v>262.65000000000003</v>
-      </c>
-      <c r="Q8" s="5">
+        <v>242</v>
+      </c>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="T8" s="5">
         <v>3003</v>
       </c>
-      <c r="R8" s="5">
+      <c r="U8" s="5">
         <v>1091</v>
       </c>
-      <c r="S8" s="5">
+      <c r="V8" s="5">
         <v>1096</v>
       </c>
-      <c r="T8" s="5">
+      <c r="W8" s="5">
         <v>1123</v>
       </c>
-      <c r="U8" s="5">
-        <f t="shared" ref="U8:U9" si="12">SUM(K8:N8)</f>
-        <v>1038.6300000000001</v>
-      </c>
-      <c r="V8" s="5">
-        <v>0</v>
-      </c>
-      <c r="W8" s="5">
-        <v>0</v>
-      </c>
       <c r="X8" s="5">
-        <v>0</v>
+        <f t="shared" ref="X8:X9" si="12">SUM(K8:N8)</f>
+        <v>985</v>
       </c>
       <c r="Y8" s="5">
         <v>0</v>
@@ -1543,8 +1568,17 @@
       <c r="AE8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:140" x14ac:dyDescent="0.3">
+      <c r="AF8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1571,7 +1605,7 @@
         <v>165</v>
       </c>
       <c r="J9" s="5">
-        <f>T9-I9-H9-G9</f>
+        <f>W9-I9-H9-G9</f>
         <v>140</v>
       </c>
       <c r="K9" s="5">
@@ -1581,71 +1615,72 @@
         <v>147</v>
       </c>
       <c r="M9" s="5">
-        <f>M7*0.12</f>
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N9" s="5">
-        <f>N7*0.12</f>
-        <v>142.0848</v>
-      </c>
-      <c r="Q9" s="5">
+        <v>150</v>
+      </c>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="T9" s="5">
         <v>475</v>
       </c>
-      <c r="R9" s="5">
+      <c r="U9" s="5">
         <v>552</v>
       </c>
-      <c r="S9" s="5">
+      <c r="V9" s="5">
         <v>553</v>
       </c>
-      <c r="T9" s="5">
+      <c r="W9" s="5">
         <v>586</v>
       </c>
-      <c r="U9" s="5">
+      <c r="X9" s="5">
         <f t="shared" si="12"/>
-        <v>617.08479999999997</v>
-      </c>
-      <c r="V9" s="5">
-        <f>V7*0.12</f>
-        <v>708.92710559999978</v>
-      </c>
-      <c r="W9" s="5">
-        <f t="shared" ref="W9:AE9" si="13">W7*0.12</f>
-        <v>765.64127404799979</v>
-      </c>
-      <c r="X9" s="5">
-        <f t="shared" si="13"/>
-        <v>811.57975049087975</v>
+        <v>622</v>
       </c>
       <c r="Y9" s="5">
-        <f t="shared" si="13"/>
-        <v>852.15873801542352</v>
+        <f>Y7*0.12</f>
+        <v>640.36764000000005</v>
       </c>
       <c r="Z9" s="5">
-        <f t="shared" si="13"/>
-        <v>886.24508753604073</v>
+        <f t="shared" ref="Z9:AH9" si="13">Z7*0.12</f>
+        <v>691.59705120000035</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="13"/>
-        <v>912.83244016212234</v>
+        <v>733.09287427200036</v>
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="13"/>
-        <v>940.21741336698597</v>
+        <v>769.74751798560055</v>
       </c>
       <c r="AC9" s="5">
         <f t="shared" si="13"/>
-        <v>968.42393576799566</v>
+        <v>800.53741870502461</v>
       </c>
       <c r="AD9" s="5">
         <f t="shared" si="13"/>
-        <v>997.47665384103539</v>
+        <v>824.5535412661751</v>
       </c>
       <c r="AE9" s="5">
         <f t="shared" si="13"/>
-        <v>1027.4009534562665</v>
-      </c>
-    </row>
-    <row r="10" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>849.2901475041607</v>
+      </c>
+      <c r="AF9" s="5">
+        <f t="shared" si="13"/>
+        <v>874.76885192928546</v>
+      </c>
+      <c r="AG9" s="5">
+        <f t="shared" si="13"/>
+        <v>901.01191748716394</v>
+      </c>
+      <c r="AH9" s="5">
+        <f t="shared" si="13"/>
+        <v>928.04227501177979</v>
+      </c>
+    </row>
+    <row r="10" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1691,74 +1726,77 @@
       </c>
       <c r="M10" s="8">
         <f t="shared" ref="M10:N10" si="15">M7-M8-M9</f>
-        <v>958.02</v>
+        <v>1086</v>
       </c>
       <c r="N10" s="8">
         <f t="shared" si="15"/>
-        <v>779.3051999999999</v>
-      </c>
-      <c r="Q10" s="8">
-        <f t="shared" ref="Q10:V10" si="16">Q7-Q8-Q9</f>
+        <v>598</v>
+      </c>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="T10" s="8">
+        <f t="shared" ref="T10:Y10" si="16">T7-T8-T9</f>
         <v>-547</v>
       </c>
-      <c r="R10" s="8">
+      <c r="U10" s="8">
         <f t="shared" si="16"/>
         <v>494</v>
       </c>
-      <c r="S10" s="8">
+      <c r="V10" s="8">
         <f t="shared" si="16"/>
         <v>1583</v>
       </c>
-      <c r="T10" s="8">
+      <c r="W10" s="8">
         <f t="shared" si="16"/>
         <v>4281</v>
       </c>
-      <c r="U10" s="8">
+      <c r="X10" s="8">
         <f t="shared" si="16"/>
-        <v>3139.3252000000007</v>
-      </c>
-      <c r="V10" s="8">
+        <v>3086</v>
+      </c>
+      <c r="Y10" s="8">
         <f t="shared" si="16"/>
-        <v>5198.7987743999984</v>
-      </c>
-      <c r="W10" s="8">
-        <f t="shared" ref="W10:AE10" si="17">W7-W8-W9</f>
-        <v>5614.702676351998</v>
-      </c>
-      <c r="X10" s="8">
-        <f t="shared" si="17"/>
-        <v>5951.5848369331188</v>
-      </c>
-      <c r="Y10" s="8">
-        <f t="shared" si="17"/>
-        <v>6249.1640787797733</v>
+        <v>4696.0293600000005</v>
       </c>
       <c r="Z10" s="8">
-        <f t="shared" si="17"/>
-        <v>6499.1306419309658</v>
+        <f t="shared" ref="Z10:AH10" si="17">Z7-Z8-Z9</f>
+        <v>5071.7117088000032</v>
       </c>
       <c r="AA10" s="8">
         <f t="shared" si="17"/>
-        <v>6694.1045611888976</v>
+        <v>5376.0144113280021</v>
       </c>
       <c r="AB10" s="8">
         <f t="shared" si="17"/>
-        <v>6894.9276980245641</v>
+        <v>5644.8151318944037</v>
       </c>
       <c r="AC10" s="8">
         <f t="shared" si="17"/>
-        <v>7101.7755289653023</v>
+        <v>5870.6077371701804</v>
       </c>
       <c r="AD10" s="8">
         <f t="shared" si="17"/>
-        <v>7314.8287948342604</v>
+        <v>6046.7259692852849</v>
       </c>
       <c r="AE10" s="8">
         <f t="shared" si="17"/>
-        <v>7534.2736586792871</v>
-      </c>
-    </row>
-    <row r="11" spans="2:140" x14ac:dyDescent="0.3">
+        <v>6228.1277483638451</v>
+      </c>
+      <c r="AF10" s="8">
+        <f t="shared" si="17"/>
+        <v>6414.9715808147603</v>
+      </c>
+      <c r="AG10" s="8">
+        <f t="shared" si="17"/>
+        <v>6607.4207282392026</v>
+      </c>
+      <c r="AH10" s="8">
+        <f t="shared" si="17"/>
+        <v>6805.6433500863859</v>
+      </c>
+    </row>
+    <row r="11" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -1772,7 +1810,7 @@
         <v>82</v>
       </c>
       <c r="F11" s="5">
-        <f t="shared" ref="F11:F12" si="18">S11-E11-D11-C11</f>
+        <f t="shared" ref="F11:F12" si="18">V11-E11-D11-C11</f>
         <v>139</v>
       </c>
       <c r="G11" s="5">
@@ -1785,7 +1823,7 @@
         <v>147</v>
       </c>
       <c r="J11" s="5">
-        <f>T11-I11-H11-G11</f>
+        <f>W11-I11-H11-G11</f>
         <v>90</v>
       </c>
       <c r="K11" s="5">
@@ -1795,72 +1833,73 @@
         <v>118</v>
       </c>
       <c r="M11" s="5">
-        <f>I11*1.02</f>
-        <v>149.94</v>
+        <v>134</v>
       </c>
       <c r="N11" s="5">
-        <f>J11*1.02</f>
-        <v>91.8</v>
-      </c>
-      <c r="Q11" s="5">
+        <v>113</v>
+      </c>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="T11" s="5">
         <f>282+15</f>
         <v>297</v>
       </c>
-      <c r="R11" s="5">
+      <c r="U11" s="5">
         <v>251</v>
       </c>
-      <c r="S11" s="5">
+      <c r="V11" s="5">
         <v>431</v>
       </c>
-      <c r="T11" s="5">
+      <c r="W11" s="5">
         <v>506</v>
       </c>
-      <c r="U11" s="5">
-        <f t="shared" ref="U11:U12" si="19">SUM(K11:N11)</f>
-        <v>505.74</v>
-      </c>
-      <c r="V11" s="5">
-        <f>U11*1.01</f>
-        <v>510.79740000000004</v>
-      </c>
-      <c r="W11" s="5">
-        <f t="shared" ref="W11:AE11" si="20">V11*1.01</f>
-        <v>515.90537400000005</v>
-      </c>
       <c r="X11" s="5">
-        <f t="shared" si="20"/>
-        <v>521.06442774000004</v>
+        <f t="shared" ref="X11:X12" si="19">SUM(K11:N11)</f>
+        <v>511</v>
       </c>
       <c r="Y11" s="5">
-        <f t="shared" si="20"/>
-        <v>526.27507201740002</v>
+        <f>X11*1.01</f>
+        <v>516.11</v>
       </c>
       <c r="Z11" s="5">
-        <f t="shared" si="20"/>
-        <v>531.53782273757406</v>
+        <f t="shared" ref="Z11:AH11" si="20">Y11*1.01</f>
+        <v>521.27110000000005</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="20"/>
-        <v>536.85320096494979</v>
+        <v>526.48381100000006</v>
       </c>
       <c r="AB11" s="5">
         <f t="shared" si="20"/>
-        <v>542.22173297459926</v>
+        <v>531.74864911000009</v>
       </c>
       <c r="AC11" s="5">
         <f t="shared" si="20"/>
-        <v>547.64395030434525</v>
+        <v>537.06613560110009</v>
       </c>
       <c r="AD11" s="5">
         <f t="shared" si="20"/>
-        <v>553.12038980738873</v>
+        <v>542.43679695711114</v>
       </c>
       <c r="AE11" s="5">
         <f t="shared" si="20"/>
-        <v>558.65159370546257</v>
-      </c>
-    </row>
-    <row r="12" spans="2:140" x14ac:dyDescent="0.3">
+        <v>547.86116492668225</v>
+      </c>
+      <c r="AF11" s="5">
+        <f t="shared" si="20"/>
+        <v>553.33977657594903</v>
+      </c>
+      <c r="AG11" s="5">
+        <f t="shared" si="20"/>
+        <v>558.87317434170848</v>
+      </c>
+      <c r="AH11" s="5">
+        <f t="shared" si="20"/>
+        <v>564.46190608512552</v>
+      </c>
+    </row>
+    <row r="12" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>17</v>
       </c>
@@ -1889,7 +1928,7 @@
         <v>-327</v>
       </c>
       <c r="J12" s="5">
-        <f>T12-I12-H12-G12</f>
+        <f>W12-I12-H12-G12</f>
         <v>-46</v>
       </c>
       <c r="K12" s="5">
@@ -1899,39 +1938,33 @@
         <v>-440</v>
       </c>
       <c r="M12" s="5">
-        <v>0</v>
+        <v>-443</v>
       </c>
       <c r="N12" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5">
+        <v>-207</v>
+      </c>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="T12" s="5">
         <f>-795-201</f>
         <v>-996</v>
       </c>
-      <c r="R12" s="5">
+      <c r="U12" s="5">
         <f>786-1</f>
         <v>785</v>
       </c>
-      <c r="S12" s="5">
+      <c r="V12" s="5">
         <f>-1268-27</f>
         <v>-1295</v>
       </c>
-      <c r="T12" s="5">
+      <c r="W12" s="5">
         <f>-670-71</f>
         <v>-741</v>
       </c>
-      <c r="U12" s="5">
+      <c r="X12" s="5">
         <f t="shared" si="19"/>
-        <v>-286</v>
-      </c>
-      <c r="V12" s="5">
-        <v>0</v>
-      </c>
-      <c r="W12" s="5">
-        <v>0</v>
-      </c>
-      <c r="X12" s="5">
-        <v>0</v>
+        <v>-936</v>
       </c>
       <c r="Y12" s="5">
         <v>0</v>
@@ -1954,8 +1987,17 @@
       <c r="AE12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AF12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
@@ -2001,74 +2043,77 @@
       </c>
       <c r="M13" s="8">
         <f t="shared" si="21"/>
-        <v>808.07999999999993</v>
+        <v>1395</v>
       </c>
       <c r="N13" s="8">
         <f t="shared" si="21"/>
-        <v>687.50519999999995</v>
-      </c>
-      <c r="Q13" s="8">
-        <f t="shared" ref="Q13:V13" si="22">Q10-Q11-Q12</f>
+        <v>692</v>
+      </c>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="T13" s="8">
+        <f t="shared" ref="T13:Y13" si="22">T10-T11-T12</f>
         <v>152</v>
       </c>
-      <c r="R13" s="8">
+      <c r="U13" s="8">
         <f t="shared" si="22"/>
         <v>-542</v>
       </c>
-      <c r="S13" s="8">
+      <c r="V13" s="8">
         <f t="shared" si="22"/>
         <v>2447</v>
       </c>
-      <c r="T13" s="8">
+      <c r="W13" s="8">
         <f t="shared" si="22"/>
         <v>4516</v>
       </c>
-      <c r="U13" s="8">
+      <c r="X13" s="8">
         <f t="shared" si="22"/>
-        <v>2919.5852000000004</v>
-      </c>
-      <c r="V13" s="8">
+        <v>3511</v>
+      </c>
+      <c r="Y13" s="8">
         <f t="shared" si="22"/>
-        <v>4688.001374399998</v>
-      </c>
-      <c r="W13" s="8">
-        <f t="shared" ref="W13:AE13" si="23">W10-W11-W12</f>
-        <v>5098.797302351998</v>
-      </c>
-      <c r="X13" s="8">
-        <f t="shared" si="23"/>
-        <v>5430.5204091931191</v>
-      </c>
-      <c r="Y13" s="8">
-        <f t="shared" si="23"/>
-        <v>5722.8890067623734</v>
+        <v>4179.9193600000008</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="23"/>
-        <v>5967.5928191933917</v>
+        <f t="shared" ref="Z13:AH13" si="23">Z10-Z11-Z12</f>
+        <v>4550.4406088000032</v>
       </c>
       <c r="AA13" s="8">
         <f t="shared" si="23"/>
-        <v>6157.2513602239478</v>
+        <v>4849.530600328002</v>
       </c>
       <c r="AB13" s="8">
         <f t="shared" si="23"/>
-        <v>6352.705965049965</v>
+        <v>5113.0664827844039</v>
       </c>
       <c r="AC13" s="8">
         <f t="shared" si="23"/>
-        <v>6554.1315786609575</v>
+        <v>5333.5416015690807</v>
       </c>
       <c r="AD13" s="8">
         <f t="shared" si="23"/>
-        <v>6761.7084050268713</v>
+        <v>5504.2891723281737</v>
       </c>
       <c r="AE13" s="8">
         <f t="shared" si="23"/>
-        <v>6975.6220649738243</v>
-      </c>
-    </row>
-    <row r="14" spans="2:140" x14ac:dyDescent="0.3">
+        <v>5680.2665834371628</v>
+      </c>
+      <c r="AF13" s="8">
+        <f t="shared" si="23"/>
+        <v>5861.6318042388111</v>
+      </c>
+      <c r="AG13" s="8">
+        <f t="shared" si="23"/>
+        <v>6048.5475538974943</v>
+      </c>
+      <c r="AH13" s="8">
+        <f t="shared" si="23"/>
+        <v>6241.1814440012604</v>
+      </c>
+    </row>
+    <row r="14" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>19</v>
       </c>
@@ -2082,7 +2127,7 @@
         <v>205</v>
       </c>
       <c r="F14" s="5">
-        <f>S14-E14-D14-C14</f>
+        <f>V14-E14-D14-C14</f>
         <v>181</v>
       </c>
       <c r="G14" s="5">
@@ -2095,7 +2140,7 @@
         <v>449</v>
       </c>
       <c r="J14" s="5">
-        <f>T14-I14-H14-G14</f>
+        <f>W14-I14-H14-G14</f>
         <v>6</v>
       </c>
       <c r="K14" s="5">
@@ -2105,71 +2150,72 @@
         <v>440</v>
       </c>
       <c r="M14" s="5">
-        <f>M13*0.17</f>
-        <v>137.37360000000001</v>
+        <v>466</v>
       </c>
       <c r="N14" s="5">
-        <f>N13*0.17</f>
-        <v>116.875884</v>
-      </c>
-      <c r="Q14" s="5">
+        <v>259</v>
+      </c>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="T14" s="5">
         <v>-225</v>
       </c>
-      <c r="R14" s="5">
+      <c r="U14" s="5">
         <v>-388</v>
       </c>
-      <c r="S14" s="5">
+      <c r="V14" s="5">
         <v>859</v>
       </c>
-      <c r="T14" s="5">
+      <c r="W14" s="5">
         <v>774</v>
       </c>
-      <c r="U14" s="5">
+      <c r="X14" s="5">
         <f>SUM(K14:N14)</f>
-        <v>716.24948400000005</v>
-      </c>
-      <c r="V14" s="5">
-        <f>V13*0.17</f>
-        <v>796.96023364799976</v>
-      </c>
-      <c r="W14" s="5">
-        <f t="shared" ref="W14:AE14" si="24">W13*0.17</f>
-        <v>866.79554139983975</v>
-      </c>
-      <c r="X14" s="5">
-        <f t="shared" si="24"/>
-        <v>923.18846956283028</v>
+        <v>1187</v>
       </c>
       <c r="Y14" s="5">
-        <f t="shared" si="24"/>
-        <v>972.89113114960355</v>
+        <f>Y13*0.17</f>
+        <v>710.58629120000023</v>
       </c>
       <c r="Z14" s="5">
-        <f t="shared" si="24"/>
-        <v>1014.4907792628767</v>
+        <f t="shared" ref="Z14:AH14" si="24">Z13*0.17</f>
+        <v>773.57490349600062</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="24"/>
-        <v>1046.7327312380712</v>
+        <v>824.42020205576046</v>
       </c>
       <c r="AB14" s="5">
         <f t="shared" si="24"/>
-        <v>1079.9600140584942</v>
+        <v>869.22130207334874</v>
       </c>
       <c r="AC14" s="5">
         <f t="shared" si="24"/>
-        <v>1114.2023683723628</v>
+        <v>906.70207226674381</v>
       </c>
       <c r="AD14" s="5">
         <f t="shared" si="24"/>
-        <v>1149.4904288545681</v>
+        <v>935.7291592957896</v>
       </c>
       <c r="AE14" s="5">
         <f t="shared" si="24"/>
-        <v>1185.8557510455503</v>
-      </c>
-    </row>
-    <row r="15" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>965.64531918431771</v>
+      </c>
+      <c r="AF14" s="5">
+        <f t="shared" si="24"/>
+        <v>996.47740672059797</v>
+      </c>
+      <c r="AG14" s="5">
+        <f t="shared" si="24"/>
+        <v>1028.2530841625742</v>
+      </c>
+      <c r="AH14" s="5">
+        <f t="shared" si="24"/>
+        <v>1061.0008454802144</v>
+      </c>
+    </row>
+    <row r="15" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,510 +2261,513 @@
       </c>
       <c r="M15" s="8">
         <f t="shared" si="25"/>
-        <v>670.70639999999992</v>
+        <v>929</v>
       </c>
       <c r="N15" s="8">
         <f t="shared" si="25"/>
-        <v>570.6293159999999</v>
-      </c>
-      <c r="Q15" s="8">
-        <f t="shared" ref="Q15:V15" si="26">Q13-Q14</f>
+        <v>433</v>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="T15" s="8">
+        <f t="shared" ref="T15:Y15" si="26">T13-T14</f>
         <v>377</v>
       </c>
-      <c r="R15" s="8">
+      <c r="U15" s="8">
         <f t="shared" si="26"/>
         <v>-154</v>
       </c>
-      <c r="S15" s="8">
+      <c r="V15" s="8">
         <f t="shared" si="26"/>
         <v>1588</v>
       </c>
-      <c r="T15" s="8">
+      <c r="W15" s="8">
         <f t="shared" si="26"/>
         <v>3742</v>
       </c>
-      <c r="U15" s="8">
+      <c r="X15" s="8">
         <f t="shared" si="26"/>
-        <v>2203.3357160000005</v>
-      </c>
-      <c r="V15" s="8">
+        <v>2324</v>
+      </c>
+      <c r="Y15" s="8">
         <f t="shared" si="26"/>
-        <v>3891.0411407519982</v>
-      </c>
-      <c r="W15" s="8">
-        <f t="shared" ref="W15:AE15" si="27">W13-W14</f>
-        <v>4232.0017609521583</v>
-      </c>
-      <c r="X15" s="8">
-        <f t="shared" si="27"/>
-        <v>4507.3319396302886</v>
-      </c>
-      <c r="Y15" s="8">
-        <f t="shared" si="27"/>
-        <v>4749.9978756127693</v>
+        <v>3469.3330688000005</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="27"/>
-        <v>4953.1020399305153</v>
+        <f t="shared" ref="Z15:AH15" si="27">Z13-Z14</f>
+        <v>3776.8657053040024</v>
       </c>
       <c r="AA15" s="8">
         <f t="shared" si="27"/>
-        <v>5110.5186289858766</v>
+        <v>4025.1103982722416</v>
       </c>
       <c r="AB15" s="8">
         <f t="shared" si="27"/>
-        <v>5272.7459509914706</v>
+        <v>4243.845180711055</v>
       </c>
       <c r="AC15" s="8">
         <f t="shared" si="27"/>
-        <v>5439.9292102885947</v>
+        <v>4426.8395293023368</v>
       </c>
       <c r="AD15" s="8">
         <f t="shared" si="27"/>
-        <v>5612.2179761723037</v>
+        <v>4568.5600130323837</v>
       </c>
       <c r="AE15" s="8">
         <f t="shared" si="27"/>
-        <v>5789.766313928274</v>
-      </c>
-      <c r="AF15" s="1">
-        <f>AE15*(1+$AH$20)</f>
-        <v>5731.8686507889915</v>
-      </c>
-      <c r="AG15" s="1">
-        <f t="shared" ref="AG15:CR15" si="28">AF15*(1+$AH$20)</f>
-        <v>5674.5499642811019</v>
-      </c>
-      <c r="AH15" s="1">
-        <f t="shared" si="28"/>
-        <v>5617.8044646382905</v>
+        <v>4714.6212642528453</v>
+      </c>
+      <c r="AF15" s="8">
+        <f t="shared" si="27"/>
+        <v>4865.154397518213</v>
+      </c>
+      <c r="AG15" s="8">
+        <f t="shared" si="27"/>
+        <v>5020.2944697349203</v>
+      </c>
+      <c r="AH15" s="8">
+        <f t="shared" si="27"/>
+        <v>5180.1805985210458</v>
       </c>
       <c r="AI15" s="1">
-        <f t="shared" si="28"/>
-        <v>5561.6264199919078</v>
+        <f>AH15*(1+$AK$20)</f>
+        <v>5128.3787925358356</v>
       </c>
       <c r="AJ15" s="1">
-        <f t="shared" si="28"/>
-        <v>5506.0101557919888</v>
+        <f t="shared" ref="AJ15:CU15" si="28">AI15*(1+$AK$20)</f>
+        <v>5077.0950046104772</v>
       </c>
       <c r="AK15" s="1">
         <f t="shared" si="28"/>
-        <v>5450.9500542340693</v>
+        <v>5026.3240545643721</v>
       </c>
       <c r="AL15" s="1">
         <f t="shared" si="28"/>
-        <v>5396.4405536917284</v>
+        <v>4976.0608140187287</v>
       </c>
       <c r="AM15" s="1">
         <f t="shared" si="28"/>
-        <v>5342.4761481548112</v>
+        <v>4926.3002058785414</v>
       </c>
       <c r="AN15" s="1">
         <f t="shared" si="28"/>
-        <v>5289.0513866732626</v>
+        <v>4877.0372038197556</v>
       </c>
       <c r="AO15" s="1">
         <f t="shared" si="28"/>
-        <v>5236.1608728065303</v>
+        <v>4828.2668317815578</v>
       </c>
       <c r="AP15" s="1">
         <f t="shared" si="28"/>
-        <v>5183.7992640784651</v>
+        <v>4779.9841634637423</v>
       </c>
       <c r="AQ15" s="1">
         <f t="shared" si="28"/>
-        <v>5131.9612714376808</v>
+        <v>4732.1843218291051</v>
       </c>
       <c r="AR15" s="1">
         <f t="shared" si="28"/>
-        <v>5080.6416587233043</v>
+        <v>4684.8624786108139</v>
       </c>
       <c r="AS15" s="1">
         <f t="shared" si="28"/>
-        <v>5029.8352421360714</v>
+        <v>4638.0138538247056</v>
       </c>
       <c r="AT15" s="1">
         <f t="shared" si="28"/>
-        <v>4979.5368897147109</v>
+        <v>4591.6337152864589</v>
       </c>
       <c r="AU15" s="1">
         <f t="shared" si="28"/>
-        <v>4929.7415208175635</v>
+        <v>4545.7173781335941</v>
       </c>
       <c r="AV15" s="1">
         <f t="shared" si="28"/>
-        <v>4880.4441056093874</v>
+        <v>4500.2602043522584</v>
       </c>
       <c r="AW15" s="1">
         <f t="shared" si="28"/>
-        <v>4831.6396645532932</v>
+        <v>4455.2576023087358</v>
       </c>
       <c r="AX15" s="1">
         <f t="shared" si="28"/>
-        <v>4783.3232679077601</v>
+        <v>4410.7050262856483</v>
       </c>
       <c r="AY15" s="1">
         <f t="shared" si="28"/>
-        <v>4735.4900352286822</v>
+        <v>4366.597976022792</v>
       </c>
       <c r="AZ15" s="1">
         <f t="shared" si="28"/>
-        <v>4688.1351348763956</v>
+        <v>4322.9319962625641</v>
       </c>
       <c r="BA15" s="1">
         <f t="shared" si="28"/>
-        <v>4641.2537835276316</v>
+        <v>4279.7026762999385</v>
       </c>
       <c r="BB15" s="1">
         <f t="shared" si="28"/>
-        <v>4594.8412456923552</v>
+        <v>4236.9056495369387</v>
       </c>
       <c r="BC15" s="1">
         <f t="shared" si="28"/>
-        <v>4548.8928332354317</v>
+        <v>4194.5365930415692</v>
       </c>
       <c r="BD15" s="1">
         <f t="shared" si="28"/>
-        <v>4503.4039049030771</v>
+        <v>4152.5912271111538</v>
       </c>
       <c r="BE15" s="1">
         <f t="shared" si="28"/>
-        <v>4458.3698658540461</v>
+        <v>4111.0653148400424</v>
       </c>
       <c r="BF15" s="1">
         <f t="shared" si="28"/>
-        <v>4413.7861671955052</v>
+        <v>4069.9546616916418</v>
       </c>
       <c r="BG15" s="1">
         <f t="shared" si="28"/>
-        <v>4369.6483055235503</v>
+        <v>4029.2551150747254</v>
       </c>
       <c r="BH15" s="1">
         <f t="shared" si="28"/>
-        <v>4325.9518224683152</v>
+        <v>3988.962563923978</v>
       </c>
       <c r="BI15" s="1">
         <f t="shared" si="28"/>
-        <v>4282.692304243632</v>
+        <v>3949.072938284738</v>
       </c>
       <c r="BJ15" s="1">
         <f t="shared" si="28"/>
-        <v>4239.8653812011953</v>
+        <v>3909.5822089018907</v>
       </c>
       <c r="BK15" s="1">
         <f t="shared" si="28"/>
-        <v>4197.4667273891837</v>
+        <v>3870.4863868128718</v>
       </c>
       <c r="BL15" s="1">
         <f t="shared" si="28"/>
-        <v>4155.4920601152917</v>
+        <v>3831.7815229447433</v>
       </c>
       <c r="BM15" s="1">
         <f t="shared" si="28"/>
-        <v>4113.9371395141388</v>
+        <v>3793.4637077152956</v>
       </c>
       <c r="BN15" s="1">
         <f t="shared" si="28"/>
-        <v>4072.7977681189973</v>
+        <v>3755.5290706381425</v>
       </c>
       <c r="BO15" s="1">
         <f t="shared" si="28"/>
-        <v>4032.0697904378071</v>
+        <v>3717.9737799317609</v>
       </c>
       <c r="BP15" s="1">
         <f t="shared" si="28"/>
-        <v>3991.7490925334291</v>
+        <v>3680.7940421324433</v>
       </c>
       <c r="BQ15" s="1">
         <f t="shared" si="28"/>
-        <v>3951.8316016080948</v>
+        <v>3643.9861017111189</v>
       </c>
       <c r="BR15" s="1">
         <f t="shared" si="28"/>
-        <v>3912.3132855920139</v>
+        <v>3607.5462406940078</v>
       </c>
       <c r="BS15" s="1">
         <f t="shared" si="28"/>
-        <v>3873.1901527360938</v>
+        <v>3571.4707782870678</v>
       </c>
       <c r="BT15" s="1">
         <f t="shared" si="28"/>
-        <v>3834.4582512087327</v>
+        <v>3535.7560705041969</v>
       </c>
       <c r="BU15" s="1">
         <f t="shared" si="28"/>
-        <v>3796.1136686966452</v>
+        <v>3500.3985097991549</v>
       </c>
       <c r="BV15" s="1">
         <f t="shared" si="28"/>
-        <v>3758.1525320096785</v>
+        <v>3465.3945247011634</v>
       </c>
       <c r="BW15" s="1">
         <f t="shared" si="28"/>
-        <v>3720.5710066895817</v>
+        <v>3430.7405794541519</v>
       </c>
       <c r="BX15" s="1">
         <f t="shared" si="28"/>
-        <v>3683.3652966226859</v>
+        <v>3396.4331736596105</v>
       </c>
       <c r="BY15" s="1">
         <f t="shared" si="28"/>
-        <v>3646.531643656459</v>
+        <v>3362.4688419230142</v>
       </c>
       <c r="BZ15" s="1">
         <f t="shared" si="28"/>
-        <v>3610.0663272198944</v>
+        <v>3328.8441535037841</v>
       </c>
       <c r="CA15" s="1">
         <f t="shared" si="28"/>
-        <v>3573.9656639476952</v>
+        <v>3295.5557119687464</v>
       </c>
       <c r="CB15" s="1">
         <f t="shared" si="28"/>
-        <v>3538.2260073082184</v>
+        <v>3262.600154849059</v>
       </c>
       <c r="CC15" s="1">
         <f t="shared" si="28"/>
-        <v>3502.8437472351361</v>
+        <v>3229.9741533005686</v>
       </c>
       <c r="CD15" s="1">
         <f t="shared" si="28"/>
-        <v>3467.8153097627846</v>
+        <v>3197.674411767563</v>
       </c>
       <c r="CE15" s="1">
         <f t="shared" si="28"/>
-        <v>3433.1371566651569</v>
+        <v>3165.6976676498875</v>
       </c>
       <c r="CF15" s="1">
         <f t="shared" si="28"/>
-        <v>3398.8057850985051</v>
+        <v>3134.0406909733888</v>
       </c>
       <c r="CG15" s="1">
         <f t="shared" si="28"/>
-        <v>3364.81772724752</v>
+        <v>3102.7002840636551</v>
       </c>
       <c r="CH15" s="1">
         <f t="shared" si="28"/>
-        <v>3331.1695499750449</v>
+        <v>3071.6732812230184</v>
       </c>
       <c r="CI15" s="1">
         <f t="shared" si="28"/>
-        <v>3297.8578544752945</v>
+        <v>3040.9565484107884</v>
       </c>
       <c r="CJ15" s="1">
         <f t="shared" si="28"/>
-        <v>3264.8792759305416</v>
+        <v>3010.5469829266804</v>
       </c>
       <c r="CK15" s="1">
         <f t="shared" si="28"/>
-        <v>3232.2304831712363</v>
+        <v>2980.4415130974135</v>
       </c>
       <c r="CL15" s="1">
         <f t="shared" si="28"/>
-        <v>3199.9081783395241</v>
+        <v>2950.6370979664393</v>
       </c>
       <c r="CM15" s="1">
         <f t="shared" si="28"/>
-        <v>3167.9090965561286</v>
+        <v>2921.1307269867748</v>
       </c>
       <c r="CN15" s="1">
         <f t="shared" si="28"/>
-        <v>3136.2300055905671</v>
+        <v>2891.9194197169072</v>
       </c>
       <c r="CO15" s="1">
         <f t="shared" si="28"/>
-        <v>3104.8677055346616</v>
+        <v>2863.0002255197383</v>
       </c>
       <c r="CP15" s="1">
         <f t="shared" si="28"/>
-        <v>3073.819028479315</v>
+        <v>2834.370223264541</v>
       </c>
       <c r="CQ15" s="1">
         <f t="shared" si="28"/>
-        <v>3043.0808381945217</v>
+        <v>2806.0265210318958</v>
       </c>
       <c r="CR15" s="1">
         <f t="shared" si="28"/>
-        <v>3012.6500298125766</v>
+        <v>2777.9662558215769</v>
       </c>
       <c r="CS15" s="1">
-        <f t="shared" ref="CS15:EJ15" si="29">CR15*(1+$AH$20)</f>
-        <v>2982.5235295144507</v>
+        <f t="shared" si="28"/>
+        <v>2750.1865932633609</v>
       </c>
       <c r="CT15" s="1">
-        <f t="shared" si="29"/>
-        <v>2952.6982942193063</v>
+        <f t="shared" si="28"/>
+        <v>2722.6847273307271</v>
       </c>
       <c r="CU15" s="1">
-        <f t="shared" si="29"/>
-        <v>2923.1713112771131</v>
+        <f t="shared" si="28"/>
+        <v>2695.45788005742</v>
       </c>
       <c r="CV15" s="1">
-        <f t="shared" si="29"/>
-        <v>2893.939598164342</v>
+        <f t="shared" ref="CV15:EM15" si="29">CU15*(1+$AK$20)</f>
+        <v>2668.5033012568456</v>
       </c>
       <c r="CW15" s="1">
         <f t="shared" si="29"/>
-        <v>2865.0002021826986</v>
+        <v>2641.8182682442771</v>
       </c>
       <c r="CX15" s="1">
         <f t="shared" si="29"/>
-        <v>2836.3502001608717</v>
+        <v>2615.4000855618342</v>
       </c>
       <c r="CY15" s="1">
         <f t="shared" si="29"/>
-        <v>2807.9866981592631</v>
+        <v>2589.2460847062157</v>
       </c>
       <c r="CZ15" s="1">
         <f t="shared" si="29"/>
-        <v>2779.9068311776705</v>
+        <v>2563.3536238591537</v>
       </c>
       <c r="DA15" s="1">
         <f t="shared" si="29"/>
-        <v>2752.1077628658936</v>
+        <v>2537.720087620562</v>
       </c>
       <c r="DB15" s="1">
         <f t="shared" si="29"/>
-        <v>2724.5866852372346</v>
+        <v>2512.3428867443563</v>
       </c>
       <c r="DC15" s="1">
         <f t="shared" si="29"/>
-        <v>2697.3408183848624</v>
+        <v>2487.2194578769127</v>
       </c>
       <c r="DD15" s="1">
         <f t="shared" si="29"/>
-        <v>2670.3674102010136</v>
+        <v>2462.3472632981434</v>
       </c>
       <c r="DE15" s="1">
         <f t="shared" si="29"/>
-        <v>2643.6637360990035</v>
+        <v>2437.7237906651621</v>
       </c>
       <c r="DF15" s="1">
         <f t="shared" si="29"/>
-        <v>2617.2270987380134</v>
+        <v>2413.3465527585104</v>
       </c>
       <c r="DG15" s="1">
         <f t="shared" si="29"/>
-        <v>2591.0548277506332</v>
+        <v>2389.2130872309253</v>
       </c>
       <c r="DH15" s="1">
         <f t="shared" si="29"/>
-        <v>2565.144279473127</v>
+        <v>2365.3209563586161</v>
       </c>
       <c r="DI15" s="1">
         <f t="shared" si="29"/>
-        <v>2539.4928366783956</v>
+        <v>2341.6677467950299</v>
       </c>
       <c r="DJ15" s="1">
         <f t="shared" si="29"/>
-        <v>2514.0979083116117</v>
+        <v>2318.2510693270797</v>
       </c>
       <c r="DK15" s="1">
         <f t="shared" si="29"/>
-        <v>2488.9569292284955</v>
+        <v>2295.0685586338091</v>
       </c>
       <c r="DL15" s="1">
         <f t="shared" si="29"/>
-        <v>2464.0673599362103</v>
+        <v>2272.1178730474708</v>
       </c>
       <c r="DM15" s="1">
         <f t="shared" si="29"/>
-        <v>2439.426686336848</v>
+        <v>2249.3966943169962</v>
       </c>
       <c r="DN15" s="1">
         <f t="shared" si="29"/>
-        <v>2415.0324194734794</v>
+        <v>2226.9027273738261</v>
       </c>
       <c r="DO15" s="1">
         <f t="shared" si="29"/>
-        <v>2390.8820952787446</v>
+        <v>2204.6337001000879</v>
       </c>
       <c r="DP15" s="1">
         <f t="shared" si="29"/>
-        <v>2366.9732743259569</v>
+        <v>2182.5873630990868</v>
       </c>
       <c r="DQ15" s="1">
         <f t="shared" si="29"/>
-        <v>2343.3035415826976</v>
+        <v>2160.761489468096</v>
       </c>
       <c r="DR15" s="1">
         <f t="shared" si="29"/>
-        <v>2319.8705061668707</v>
+        <v>2139.1538745734151</v>
       </c>
       <c r="DS15" s="1">
         <f t="shared" si="29"/>
-        <v>2296.6718011052021</v>
+        <v>2117.762335827681</v>
       </c>
       <c r="DT15" s="1">
         <f t="shared" si="29"/>
-        <v>2273.7050830941503</v>
+        <v>2096.5847124694042</v>
       </c>
       <c r="DU15" s="1">
         <f t="shared" si="29"/>
-        <v>2250.9680322632089</v>
+        <v>2075.6188653447102</v>
       </c>
       <c r="DV15" s="1">
         <f t="shared" si="29"/>
-        <v>2228.4583519405769</v>
+        <v>2054.862676691263</v>
       </c>
       <c r="DW15" s="1">
         <f t="shared" si="29"/>
-        <v>2206.1737684211712</v>
+        <v>2034.3140499243505</v>
       </c>
       <c r="DX15" s="1">
         <f t="shared" si="29"/>
-        <v>2184.1120307369592</v>
+        <v>2013.970909425107</v>
       </c>
       <c r="DY15" s="1">
         <f t="shared" si="29"/>
-        <v>2162.2709104295895</v>
+        <v>1993.8312003308561</v>
       </c>
       <c r="DZ15" s="1">
         <f t="shared" si="29"/>
-        <v>2140.6482013252935</v>
+        <v>1973.8928883275476</v>
       </c>
       <c r="EA15" s="1">
         <f t="shared" si="29"/>
-        <v>2119.2417193120405</v>
+        <v>1954.153959444272</v>
       </c>
       <c r="EB15" s="1">
         <f t="shared" si="29"/>
-        <v>2098.04930211892</v>
+        <v>1934.6124198498292</v>
       </c>
       <c r="EC15" s="1">
         <f t="shared" si="29"/>
-        <v>2077.0688090977305</v>
+        <v>1915.2662956513309</v>
       </c>
       <c r="ED15" s="1">
         <f t="shared" si="29"/>
-        <v>2056.2981210067533</v>
+        <v>1896.1136326948176</v>
       </c>
       <c r="EE15" s="1">
         <f t="shared" si="29"/>
-        <v>2035.7351397966856</v>
+        <v>1877.1524963678694</v>
       </c>
       <c r="EF15" s="1">
         <f t="shared" si="29"/>
-        <v>2015.3777883987188</v>
+        <v>1858.3809714041906</v>
       </c>
       <c r="EG15" s="1">
         <f t="shared" si="29"/>
-        <v>1995.2240105147316</v>
+        <v>1839.7971616901486</v>
       </c>
       <c r="EH15" s="1">
         <f t="shared" si="29"/>
-        <v>1975.2717704095842</v>
+        <v>1821.3991900732472</v>
       </c>
       <c r="EI15" s="1">
         <f t="shared" si="29"/>
-        <v>1955.5190527054883</v>
+        <v>1803.1851981725147</v>
       </c>
       <c r="EJ15" s="1">
         <f t="shared" si="29"/>
-        <v>1935.9638621784334</v>
-      </c>
-    </row>
-    <row r="16" spans="2:140" x14ac:dyDescent="0.3">
+        <v>1785.1533461907895</v>
+      </c>
+      <c r="EK15" s="1">
+        <f t="shared" si="29"/>
+        <v>1767.3018127288817</v>
+      </c>
+      <c r="EL15" s="1">
+        <f t="shared" si="29"/>
+        <v>1749.628794601593</v>
+      </c>
+      <c r="EM15" s="1">
+        <f t="shared" si="29"/>
+        <v>1732.1325066555771</v>
+      </c>
+    </row>
+    <row r="16" spans="2:143" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>2</v>
       </c>
@@ -2754,71 +2803,74 @@
         <v>312.39999999999998</v>
       </c>
       <c r="M16" s="5">
-        <f>312.4</f>
-        <v>312.39999999999998</v>
+        <f>312.3</f>
+        <v>312.3</v>
       </c>
       <c r="N16" s="5">
-        <f>312.4</f>
-        <v>312.39999999999998</v>
-      </c>
-      <c r="Q16" s="5">
+        <f>312.3</f>
+        <v>312.3</v>
+      </c>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="T16" s="5">
         <v>213.7</v>
       </c>
-      <c r="R16" s="5">
+      <c r="U16" s="5">
         <v>213.7</v>
       </c>
-      <c r="S16" s="5">
+      <c r="V16" s="5">
         <v>213.7</v>
       </c>
-      <c r="T16" s="5">
+      <c r="W16" s="5">
         <v>312.8</v>
       </c>
-      <c r="U16" s="5">
-        <f>312.4</f>
-        <v>312.39999999999998</v>
-      </c>
-      <c r="V16" s="5">
-        <f>312.4</f>
-        <v>312.39999999999998</v>
-      </c>
-      <c r="W16" s="5">
-        <f t="shared" ref="W16:AE16" si="30">312.4</f>
-        <v>312.39999999999998</v>
-      </c>
       <c r="X16" s="5">
-        <f t="shared" si="30"/>
-        <v>312.39999999999998</v>
+        <f t="shared" ref="X16:AH16" si="30">312.3</f>
+        <v>312.3</v>
       </c>
       <c r="Y16" s="5">
         <f t="shared" si="30"/>
-        <v>312.39999999999998</v>
+        <v>312.3</v>
       </c>
       <c r="Z16" s="5">
         <f t="shared" si="30"/>
-        <v>312.39999999999998</v>
+        <v>312.3</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="30"/>
-        <v>312.39999999999998</v>
+        <v>312.3</v>
       </c>
       <c r="AB16" s="5">
         <f t="shared" si="30"/>
-        <v>312.39999999999998</v>
+        <v>312.3</v>
       </c>
       <c r="AC16" s="5">
         <f t="shared" si="30"/>
-        <v>312.39999999999998</v>
+        <v>312.3</v>
       </c>
       <c r="AD16" s="5">
         <f t="shared" si="30"/>
-        <v>312.39999999999998</v>
+        <v>312.3</v>
       </c>
       <c r="AE16" s="5">
         <f t="shared" si="30"/>
-        <v>312.39999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.3">
+        <v>312.3</v>
+      </c>
+      <c r="AF16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.3</v>
+      </c>
+      <c r="AG16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.3</v>
+      </c>
+      <c r="AH16" s="5">
+        <f t="shared" si="30"/>
+        <v>312.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>21</v>
       </c>
@@ -2864,74 +2916,77 @@
       </c>
       <c r="M17" s="7">
         <f t="shared" si="31"/>
-        <v>2.1469475032010243</v>
+        <v>2.9747038104386805</v>
       </c>
       <c r="N17" s="7">
         <f t="shared" si="31"/>
-        <v>1.8265983226632521</v>
-      </c>
-      <c r="Q17" s="7">
-        <f>Q15/Q16</f>
+        <v>1.3864873519052192</v>
+      </c>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="T17" s="7">
+        <f>T15/T16</f>
         <v>1.7641553579784746</v>
       </c>
-      <c r="R17" s="7">
-        <f>R15/R16</f>
+      <c r="U17" s="7">
+        <f>U15/U16</f>
         <v>-0.72063640617688351</v>
       </c>
-      <c r="S17" s="7">
-        <f>S15/S16</f>
+      <c r="V17" s="7">
+        <f>V15/V16</f>
         <v>7.4309780065512401</v>
       </c>
-      <c r="T17" s="7">
-        <f t="shared" ref="T17:V17" si="32">T15/T16</f>
+      <c r="W17" s="7">
+        <f t="shared" ref="W17:Y17" si="32">W15/W16</f>
         <v>11.962915601023017</v>
       </c>
-      <c r="U17" s="7">
+      <c r="X17" s="7">
         <f t="shared" si="32"/>
-        <v>7.0529312291933444</v>
-      </c>
-      <c r="V17" s="7">
+        <v>7.4415626000640405</v>
+      </c>
+      <c r="Y17" s="7">
         <f t="shared" si="32"/>
-        <v>12.455317351959023</v>
-      </c>
-      <c r="W17" s="7">
-        <f t="shared" ref="W17:AE17" si="33">W15/W16</f>
-        <v>13.546740592036359</v>
-      </c>
-      <c r="X17" s="7">
-        <f t="shared" si="33"/>
-        <v>14.428079192158416</v>
-      </c>
-      <c r="Y17" s="7">
-        <f t="shared" si="33"/>
-        <v>15.204858756763027</v>
+        <v>11.108975564521295</v>
       </c>
       <c r="Z17" s="7">
-        <f t="shared" si="33"/>
-        <v>15.855000127818553</v>
+        <f t="shared" ref="Z17:AH17" si="33">Z15/Z16</f>
+        <v>12.09371023152098</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="33"/>
-        <v>16.35889445898168</v>
+        <v>12.888601979738205</v>
       </c>
       <c r="AB17" s="7">
         <f t="shared" si="33"/>
-        <v>16.878188063352979</v>
+        <v>13.589001539260503</v>
       </c>
       <c r="AC17" s="7">
         <f t="shared" si="33"/>
-        <v>17.413345743561443</v>
+        <v>14.174958467186476</v>
       </c>
       <c r="AD17" s="7">
         <f t="shared" si="33"/>
-        <v>17.964846274559232</v>
+        <v>14.628754444548138</v>
       </c>
       <c r="AE17" s="7">
         <f t="shared" si="33"/>
-        <v>18.533182823073862</v>
-      </c>
-    </row>
-    <row r="19" spans="2:34" x14ac:dyDescent="0.3">
+        <v>15.096449773464121</v>
+      </c>
+      <c r="AF17" s="7">
+        <f t="shared" si="33"/>
+        <v>15.578464289203371</v>
+      </c>
+      <c r="AG17" s="7">
+        <f t="shared" si="33"/>
+        <v>16.075230450640156</v>
+      </c>
+      <c r="AH17" s="7">
+        <f t="shared" si="33"/>
+        <v>16.587193719247665</v>
+      </c>
+    </row>
+    <row r="19" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>33</v>
       </c>
@@ -2965,59 +3020,50 @@
       </c>
       <c r="M19" s="9">
         <f t="shared" ref="M19:N19" si="35">M3/I3-1</f>
-        <v>6.8702290076335881E-2</v>
+        <v>3.0534351145037331E-3</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="35"/>
+        <v>0.12857673727238939</v>
+      </c>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="U19" s="9">
+        <f>U3/T3-1</f>
+        <v>0.24382920250394413</v>
+      </c>
+      <c r="V19" s="9">
+        <f>V3/U3-1</f>
+        <v>1.9558101472995082E-2</v>
+      </c>
+      <c r="W19" s="9">
+        <f t="shared" ref="W19:AH19" si="36">W3/V3-1</f>
+        <v>-5.4177702865398469E-2</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" si="36"/>
+        <v>8.3375763747454146E-2</v>
+      </c>
+      <c r="Y19" s="9">
+        <f t="shared" si="36"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="R19" s="9">
-        <f>R3/Q3-1</f>
-        <v>0.24382920250394413</v>
-      </c>
-      <c r="S19" s="9">
-        <f>S3/R3-1</f>
-        <v>1.9558101472995082E-2</v>
-      </c>
-      <c r="T19" s="9">
-        <f t="shared" ref="T19:AE19" si="36">T3/S3-1</f>
-        <v>-5.4177702865398469E-2</v>
-      </c>
-      <c r="U19" s="9">
-        <f t="shared" si="36"/>
-        <v>9.5095044127630812E-2</v>
-      </c>
-      <c r="V19" s="9">
-        <f t="shared" si="36"/>
-        <v>9.000000000000008E-2</v>
-      </c>
-      <c r="W19" s="9">
+      <c r="Z19" s="9">
         <f t="shared" si="36"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="X19" s="9">
+      <c r="AA19" s="9">
         <f t="shared" si="36"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="Y19" s="9">
+      <c r="AB19" s="9">
         <f t="shared" si="36"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="Z19" s="9">
+      <c r="AC19" s="9">
         <f t="shared" si="36"/>
         <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AA19" s="9">
-        <f t="shared" si="36"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AB19" s="9">
-        <f t="shared" si="36"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AC19" s="9">
-        <f t="shared" si="36"/>
-        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD19" s="9">
         <f t="shared" si="36"/>
@@ -3027,8 +3073,20 @@
         <f t="shared" si="36"/>
         <v>3.0000000000000027E-2</v>
       </c>
-    </row>
-    <row r="20" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="AF19" s="9">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AG19" s="9">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH19" s="9">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>41</v>
       </c>
@@ -3074,80 +3132,83 @@
       </c>
       <c r="M20" s="9">
         <f t="shared" ref="M20:N20" si="38">(M3-M4)/M3</f>
-        <v>0.44999999999999996</v>
+        <v>0.45707762557077625</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="38"/>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="Q20" s="9">
-        <f t="shared" ref="Q20:T20" si="39">(Q3-Q4)/Q3</f>
+        <v>0.40763911755021404</v>
+      </c>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="T20" s="9">
+        <f t="shared" ref="T20:W20" si="39">(T3-T4)/T3</f>
         <v>0.38098630973586445</v>
       </c>
-      <c r="R20" s="9">
+      <c r="U20" s="9">
         <f t="shared" si="39"/>
         <v>0.28551554828150572</v>
       </c>
-      <c r="S20" s="9">
+      <c r="V20" s="9">
         <f t="shared" si="39"/>
         <v>0.35785376033389515</v>
       </c>
-      <c r="T20" s="9">
+      <c r="W20" s="9">
         <f t="shared" si="39"/>
         <v>0.51548710115410723</v>
       </c>
-      <c r="U20" s="9">
-        <f t="shared" ref="U20:AE20" si="40">(U3-U4)/U3</f>
-        <v>0.43345357469429507</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="40"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" si="40"/>
-        <v>0.43999999999999989</v>
-      </c>
       <c r="X20" s="9">
-        <f t="shared" si="40"/>
-        <v>0.43999999999999989</v>
+        <f t="shared" ref="X20:AH20" si="40">(X3-X4)/X3</f>
+        <v>0.42501860337602321</v>
       </c>
       <c r="Y20" s="9">
         <f t="shared" si="40"/>
-        <v>0.43999999999999989</v>
+        <v>0.43000000000000005</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="40"/>
-        <v>0.44</v>
+        <v>0.4300000000000001</v>
       </c>
       <c r="AA20" s="9">
         <f t="shared" si="40"/>
-        <v>0.43999999999999995</v>
+        <v>0.43</v>
       </c>
       <c r="AB20" s="9">
         <f t="shared" si="40"/>
-        <v>0.44</v>
+        <v>0.43000000000000005</v>
       </c>
       <c r="AC20" s="9">
         <f t="shared" si="40"/>
-        <v>0.43999999999999995</v>
+        <v>0.43000000000000005</v>
       </c>
       <c r="AD20" s="9">
         <f t="shared" si="40"/>
-        <v>0.43999999999999995</v>
+        <v>0.43000000000000005</v>
       </c>
       <c r="AE20" s="9">
         <f t="shared" si="40"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="AG20" t="s">
+        <v>0.43000000000000005</v>
+      </c>
+      <c r="AF20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.43000000000000005</v>
+      </c>
+      <c r="AG20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.4300000000000001</v>
+      </c>
+      <c r="AH20" s="9">
+        <f t="shared" si="40"/>
+        <v>0.4300000000000001</v>
+      </c>
+      <c r="AJ20" t="s">
         <v>43</v>
       </c>
-      <c r="AH20" s="9">
+      <c r="AK20" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="21" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>42</v>
       </c>
@@ -3193,80 +3254,83 @@
       </c>
       <c r="M21" s="9">
         <f t="shared" ref="M21:N21" si="42">(M3-M5)/M3</f>
-        <v>0.75</v>
+        <v>0.77001522070015216</v>
       </c>
       <c r="N21" s="9">
         <f t="shared" si="42"/>
-        <v>0.75</v>
-      </c>
-      <c r="Q21" s="9">
-        <f t="shared" ref="Q21:T21" si="43">(Q3-Q5)/Q3</f>
+        <v>0.75535067500823183</v>
+      </c>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="T21" s="9">
+        <f t="shared" ref="T21:W21" si="43">(T3-T5)/T3</f>
         <v>0.76818158684920357</v>
       </c>
-      <c r="R21" s="9">
+      <c r="U21" s="9">
         <f t="shared" si="43"/>
         <v>0.80192307692307696</v>
       </c>
-      <c r="S21" s="9">
+      <c r="V21" s="9">
         <f t="shared" si="43"/>
         <v>0.77185167348904404</v>
       </c>
-      <c r="T21" s="9">
+      <c r="W21" s="9">
         <f t="shared" si="43"/>
         <v>0.7386710794297352</v>
       </c>
-      <c r="U21" s="9">
-        <f t="shared" ref="U21:AE21" si="44">(U3-U5)/U3</f>
-        <v>0.75233443888225904</v>
-      </c>
-      <c r="V21" s="9">
-        <f t="shared" si="44"/>
-        <v>0.76999999999999991</v>
-      </c>
-      <c r="W21" s="9">
-        <f t="shared" si="44"/>
-        <v>0.77</v>
-      </c>
       <c r="X21" s="9">
-        <f t="shared" si="44"/>
-        <v>0.77</v>
+        <f t="shared" ref="X21:AH21" si="44">(X3-X5)/X3</f>
+        <v>0.75878275173305132</v>
       </c>
       <c r="Y21" s="9">
         <f t="shared" si="44"/>
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="Z21" s="9">
         <f t="shared" si="44"/>
-        <v>0.76999999999999991</v>
+        <v>0.76</v>
       </c>
       <c r="AA21" s="9">
         <f t="shared" si="44"/>
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AB21" s="9">
         <f t="shared" si="44"/>
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AC21" s="9">
         <f t="shared" si="44"/>
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AD21" s="9">
         <f t="shared" si="44"/>
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AE21" s="9">
         <f t="shared" si="44"/>
-        <v>0.77</v>
-      </c>
-      <c r="AG21" t="s">
+        <v>0.76</v>
+      </c>
+      <c r="AF21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.76</v>
+      </c>
+      <c r="AG21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="AH21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.76</v>
+      </c>
+      <c r="AJ21" t="s">
         <v>44</v>
       </c>
-      <c r="AH21" s="9">
+      <c r="AK21" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>34</v>
       </c>
@@ -3312,81 +3376,84 @@
       </c>
       <c r="M22" s="9">
         <f t="shared" ref="M22:N22" si="46">M7/M3</f>
-        <v>0.2</v>
+        <v>0.22709284627092846</v>
       </c>
       <c r="N22" s="9">
         <f t="shared" si="46"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="Q22" s="9">
-        <f>Q7/Q3</f>
+        <v>0.16298979255844584</v>
+      </c>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="T22" s="9">
+        <f>T7/T3</f>
         <v>0.14916789658506793</v>
       </c>
-      <c r="R22" s="9">
-        <f>R7/R3</f>
+      <c r="U22" s="9">
+        <f>U7/U3</f>
         <v>8.7438625204582648E-2</v>
       </c>
-      <c r="S22" s="9">
-        <f>S7/S3</f>
+      <c r="V22" s="9">
+        <f>V7/V3</f>
         <v>0.12970543382293925</v>
       </c>
-      <c r="T22" s="9">
-        <f t="shared" ref="T22:AE22" si="47">T7/T3</f>
+      <c r="W22" s="9">
+        <f t="shared" ref="W22:AH22" si="47">W7/W3</f>
         <v>0.25415818058384249</v>
-      </c>
-      <c r="U22" s="9">
-        <f t="shared" si="47"/>
-        <v>0.18578801357655411</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="47"/>
-        <v>0.20999999999999991</v>
-      </c>
-      <c r="W22" s="9">
-        <f t="shared" si="47"/>
-        <v>0.20999999999999991</v>
       </c>
       <c r="X22" s="9">
         <f t="shared" si="47"/>
-        <v>0.20999999999999991</v>
+        <v>0.18380135510907453</v>
       </c>
       <c r="Y22" s="9">
         <f t="shared" si="47"/>
-        <v>0.20999999999999985</v>
+        <v>0.19</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" si="47"/>
-        <v>0.20999999999999994</v>
+        <v>0.19000000000000009</v>
       </c>
       <c r="AA22" s="9">
         <f t="shared" si="47"/>
-        <v>0.21</v>
+        <v>0.19000000000000003</v>
       </c>
       <c r="AB22" s="9">
         <f t="shared" si="47"/>
-        <v>0.21</v>
+        <v>0.19000000000000009</v>
       </c>
       <c r="AC22" s="9">
         <f t="shared" si="47"/>
-        <v>0.21000000000000002</v>
+        <v>0.19000000000000009</v>
       </c>
       <c r="AD22" s="9">
         <f t="shared" si="47"/>
-        <v>0.20999999999999996</v>
+        <v>0.19</v>
       </c>
       <c r="AE22" s="9">
         <f t="shared" si="47"/>
-        <v>0.20999999999999994</v>
-      </c>
-      <c r="AG22" t="s">
+        <v>0.19000000000000006</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.19000000000000006</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="AH22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="AJ22" t="s">
         <v>45</v>
       </c>
-      <c r="AH22" s="5">
-        <f>NPV(AH21,U15:EJ15)</f>
-        <v>67884.566725731507</v>
-      </c>
-    </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="AK22" s="5">
+        <f>NPV(AK21,X15:EM15)</f>
+        <v>61029.377841935682</v>
+      </c>
+    </row>
+    <row r="23" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>35</v>
       </c>
@@ -3432,81 +3499,84 @@
       </c>
       <c r="M23" s="9">
         <f t="shared" ref="M23:N23" si="49">M10/M3</f>
-        <v>0.13686000000000001</v>
+        <v>0.16529680365296803</v>
       </c>
       <c r="N23" s="9">
         <f t="shared" si="49"/>
-        <v>0.13163494476537951</v>
-      </c>
-      <c r="Q23" s="9">
-        <f>Q10/Q3</f>
+        <v>9.8452420151465256E-2</v>
+      </c>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="T23" s="9">
+        <f>T10/T3</f>
         <v>-2.7838566848185659E-2</v>
       </c>
-      <c r="R23" s="9">
-        <f>R10/R3</f>
+      <c r="U23" s="9">
+        <f>U10/U3</f>
         <v>2.021276595744681E-2</v>
       </c>
-      <c r="S23" s="9">
-        <f>S10/S3</f>
+      <c r="V23" s="9">
+        <f>V10/V3</f>
         <v>6.3528373063648766E-2</v>
       </c>
-      <c r="T23" s="9">
-        <f t="shared" ref="T23:AE23" si="50">T10/T3</f>
+      <c r="W23" s="9">
+        <f t="shared" ref="W23:AH23" si="50">W10/W3</f>
         <v>0.18164460285132383</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="50"/>
-        <v>0.12163589727694003</v>
-      </c>
-      <c r="V23" s="9">
-        <f t="shared" si="50"/>
-        <v>0.18479999999999994</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" si="50"/>
-        <v>0.18479999999999991</v>
       </c>
       <c r="X23" s="9">
         <f t="shared" si="50"/>
-        <v>0.18479999999999991</v>
+        <v>0.12086319664747582</v>
       </c>
       <c r="Y23" s="9">
         <f t="shared" si="50"/>
-        <v>0.18479999999999988</v>
+        <v>0.16719999999999999</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" si="50"/>
-        <v>0.18479999999999994</v>
+        <v>0.16720000000000007</v>
       </c>
       <c r="AA23" s="9">
         <f t="shared" si="50"/>
-        <v>0.18479999999999999</v>
+        <v>0.16720000000000002</v>
       </c>
       <c r="AB23" s="9">
         <f t="shared" si="50"/>
-        <v>0.18479999999999999</v>
+        <v>0.16720000000000007</v>
       </c>
       <c r="AC23" s="9">
         <f t="shared" si="50"/>
-        <v>0.18480000000000002</v>
+        <v>0.16720000000000007</v>
       </c>
       <c r="AD23" s="9">
         <f t="shared" si="50"/>
-        <v>0.18479999999999996</v>
+        <v>0.16720000000000002</v>
       </c>
       <c r="AE23" s="9">
         <f t="shared" si="50"/>
-        <v>0.18479999999999994</v>
-      </c>
-      <c r="AG23" t="s">
+        <v>0.16720000000000004</v>
+      </c>
+      <c r="AF23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.16720000000000004</v>
+      </c>
+      <c r="AG23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.16720000000000002</v>
+      </c>
+      <c r="AH23" s="9">
+        <f t="shared" si="50"/>
+        <v>0.16720000000000018</v>
+      </c>
+      <c r="AJ23" t="s">
         <v>47</v>
       </c>
-      <c r="AH23" s="5">
+      <c r="AK23" s="5">
         <f>Main!D8</f>
-        <v>-6249</v>
-      </c>
-    </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.3">
+        <v>-5244</v>
+      </c>
+    </row>
+    <row r="24" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>19</v>
       </c>
@@ -3552,43 +3622,34 @@
       </c>
       <c r="M24" s="9">
         <f t="shared" ref="M24:N24" si="52">M14/M13</f>
-        <v>0.17000000000000004</v>
+        <v>0.33405017921146951</v>
       </c>
       <c r="N24" s="9">
         <f t="shared" si="52"/>
-        <v>0.17</v>
-      </c>
-      <c r="Q24" s="9">
-        <f>Q14/Q13</f>
+        <v>0.37427745664739887</v>
+      </c>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="T24" s="9">
+        <f>T14/T13</f>
         <v>-1.4802631578947369</v>
       </c>
-      <c r="R24" s="9">
-        <f>R14/R13</f>
+      <c r="U24" s="9">
+        <f>U14/U13</f>
         <v>0.71586715867158668</v>
       </c>
-      <c r="S24" s="9">
-        <f>S14/S13</f>
+      <c r="V24" s="9">
+        <f>V14/V13</f>
         <v>0.35104209235798939</v>
       </c>
-      <c r="T24" s="9">
-        <f t="shared" ref="T24:AE24" si="53">T14/T13</f>
+      <c r="W24" s="9">
+        <f t="shared" ref="W24:AH24" si="53">W14/W13</f>
         <v>0.17139061116031887</v>
-      </c>
-      <c r="U24" s="9">
-        <f t="shared" si="53"/>
-        <v>0.24532576887977098</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" si="53"/>
-        <v>0.17</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" si="53"/>
-        <v>0.17</v>
       </c>
       <c r="X24" s="9">
         <f t="shared" si="53"/>
-        <v>0.17</v>
+        <v>0.33808031899743662</v>
       </c>
       <c r="Y24" s="9">
         <f t="shared" si="53"/>
@@ -3612,21 +3673,33 @@
       </c>
       <c r="AD24" s="9">
         <f t="shared" si="53"/>
-        <v>0.16999999999999998</v>
+        <v>0.17</v>
       </c>
       <c r="AE24" s="9">
         <f t="shared" si="53"/>
         <v>0.17</v>
       </c>
-      <c r="AG24" t="s">
+      <c r="AF24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="53"/>
+        <v>0.17</v>
+      </c>
+      <c r="AJ24" t="s">
         <v>46</v>
       </c>
-      <c r="AH24" s="5">
-        <f>AH22+AH23</f>
-        <v>61635.566725731507</v>
-      </c>
-    </row>
-    <row r="25" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="AK24" s="5">
+        <f>AK22+AK23</f>
+        <v>55785.377841935682</v>
+      </c>
+    </row>
+    <row r="25" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>36</v>
       </c>
@@ -3672,125 +3745,128 @@
       </c>
       <c r="M25" s="9">
         <f t="shared" ref="M25:N25" si="55">M15/M3</f>
-        <v>9.5815199999999989E-2</v>
+        <v>0.14140030441400303</v>
       </c>
       <c r="N25" s="9">
         <f t="shared" si="55"/>
-        <v>9.638683085030908E-2</v>
-      </c>
-      <c r="Q25" s="9">
-        <f>Q15/Q3</f>
+        <v>7.1287454725057625E-2</v>
+      </c>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="T25" s="9">
+        <f>T15/T3</f>
         <v>1.9186727059901269E-2</v>
       </c>
-      <c r="R25" s="9">
-        <f>R15/R3</f>
+      <c r="U25" s="9">
+        <f>U15/U3</f>
         <v>-6.3011456628477907E-3</v>
       </c>
-      <c r="S25" s="9">
-        <f>S15/S3</f>
+      <c r="V25" s="9">
+        <f>V15/V3</f>
         <v>6.3729031222409499E-2</v>
       </c>
-      <c r="T25" s="9">
-        <f t="shared" ref="T25:AE25" si="56">T15/T3</f>
+      <c r="W25" s="9">
+        <f t="shared" ref="W25:AH25" si="56">W15/W3</f>
         <v>0.15877460964019008</v>
-      </c>
-      <c r="U25" s="9">
-        <f t="shared" si="56"/>
-        <v>8.5370167072206821E-2</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="56"/>
-        <v>0.13831356704010098</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" si="56"/>
-        <v>0.13929035436157591</v>
       </c>
       <c r="X25" s="9">
         <f t="shared" si="56"/>
-        <v>0.13995514896716196</v>
+        <v>9.1019465006070568E-2</v>
       </c>
       <c r="Y25" s="9">
         <f t="shared" si="56"/>
-        <v>0.14046672424460335</v>
+        <v>0.12352403373886914</v>
       </c>
       <c r="Z25" s="9">
         <f t="shared" si="56"/>
-        <v>0.14083933796831677</v>
+        <v>0.12451258710764619</v>
       </c>
       <c r="AA25" s="9">
         <f t="shared" si="56"/>
-        <v>0.14108292363883496</v>
+        <v>0.1251853896025685</v>
       </c>
       <c r="AB25" s="9">
         <f t="shared" si="56"/>
-        <v>0.14132177949050806</v>
+        <v>0.12570312714151829</v>
       </c>
       <c r="AC25" s="9">
         <f t="shared" si="56"/>
-        <v>0.1415559973644788</v>
+        <v>0.12608022924320528</v>
       </c>
       <c r="AD25" s="9">
         <f t="shared" si="56"/>
-        <v>0.14178566731856657</v>
+        <v>0.12632674906372551</v>
       </c>
       <c r="AE25" s="9">
         <f t="shared" si="56"/>
-        <v>0.14201087766189532</v>
-      </c>
-      <c r="AG25" t="s">
+        <v>0.12656848209161439</v>
+      </c>
+      <c r="AF25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.12680552127430147</v>
+      </c>
+      <c r="AG25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.12703795775441212</v>
+      </c>
+      <c r="AH25" s="9">
+        <f t="shared" si="56"/>
+        <v>0.127265880904812</v>
+      </c>
+      <c r="AJ25" t="s">
         <v>48</v>
       </c>
-      <c r="AH25" s="6">
-        <f>AH24/AE16</f>
-        <v>197.29694854587552</v>
-      </c>
-    </row>
-    <row r="26" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="AG26" t="s">
+      <c r="AK25" s="6">
+        <f>AK24/AH16</f>
+        <v>178.62753071385103</v>
+      </c>
+    </row>
+    <row r="26" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AJ26" t="s">
         <v>49</v>
       </c>
-      <c r="AH26" s="6">
+      <c r="AK26" s="6">
         <f>Main!D3</f>
-        <v>384.26</v>
-      </c>
-    </row>
-    <row r="27" spans="2:34" x14ac:dyDescent="0.3">
-      <c r="AG27" s="1" t="s">
+        <v>312.64</v>
+      </c>
+    </row>
+    <row r="27" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AJ27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AH27" s="10">
-        <f>AH25/AH26-1</f>
-        <v>-0.48655350922324592</v>
-      </c>
-    </row>
-    <row r="28" spans="2:34" x14ac:dyDescent="0.3">
+      <c r="AK27" s="10">
+        <f>AK25/AK26-1</f>
+        <v>-0.42864786747104966</v>
+      </c>
+    </row>
+    <row r="28" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>4</v>
       </c>
-      <c r="AG28" t="s">
+      <c r="AJ28" t="s">
         <v>51</v>
       </c>
-      <c r="AH28" s="2" t="s">
+      <c r="AK28" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>56</v>
       </c>
